--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F23B53-6176-4719-B734-19A616B6D4A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589DD8EC-E972-2E43-88AE-3369978D2416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16960" yWindow="780" windowWidth="19040" windowHeight="20900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="75">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -290,29 +290,33 @@
   <si>
     <t>PNY</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>`</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -325,7 +329,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -362,46 +366,52 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -679,22 +689,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:25" s="3" customFormat="1">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="12" t="s">
@@ -749,9 +759,9 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
+    <row r="2" spans="1:25">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
       <c r="C2" s="12"/>
       <c r="D2" s="11"/>
       <c r="E2" s="4" t="s">
@@ -800,12 +810,12 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+    <row r="3" spans="1:25">
+      <c r="A3" s="14">
         <v>46034</v>
       </c>
-      <c r="B3" s="6">
-        <v>46034</v>
+      <c r="B3" s="14">
+        <v>46048</v>
       </c>
       <c r="C3" s="7">
         <v>0.61111111111111105</v>
@@ -859,12 +869,12 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+    <row r="4" spans="1:25">
+      <c r="A4" s="14">
         <v>46048</v>
       </c>
-      <c r="B4" s="6">
-        <v>46048</v>
+      <c r="B4" s="14">
+        <v>46055</v>
       </c>
       <c r="C4" s="7">
         <v>0.61111111111111105</v>
@@ -918,12 +928,12 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+    <row r="5" spans="1:25">
+      <c r="A5" s="14">
         <v>46055</v>
       </c>
-      <c r="B5" s="6">
-        <v>46055</v>
+      <c r="B5" s="14">
+        <v>46062</v>
       </c>
       <c r="C5" s="7">
         <v>0.61111111111111105</v>
@@ -968,12 +978,12 @@
         <v>4.9729999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+    <row r="6" spans="1:25">
+      <c r="A6" s="14">
         <v>46062</v>
       </c>
-      <c r="B6" s="6">
-        <v>46062</v>
+      <c r="B6" s="14">
+        <v>46076</v>
       </c>
       <c r="C6" s="7">
         <v>0.61111111111111105</v>
@@ -1016,6 +1026,56 @@
       </c>
       <c r="P6" s="9">
         <v>5.2450000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" s="14">
+        <v>46076</v>
+      </c>
+      <c r="B7" s="14">
+        <v>46083</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F7" s="9">
+        <v>1.9</v>
+      </c>
+      <c r="G7" s="9">
+        <v>2.1890000000000001</v>
+      </c>
+      <c r="H7" s="9">
+        <v>2.4</v>
+      </c>
+      <c r="I7" s="9">
+        <v>1.65</v>
+      </c>
+      <c r="J7" s="9">
+        <v>1.8180000000000001</v>
+      </c>
+      <c r="K7" s="9">
+        <v>11</v>
+      </c>
+      <c r="L7" s="9">
+        <v>8</v>
+      </c>
+      <c r="M7" s="9">
+        <v>8.875</v>
+      </c>
+      <c r="N7" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="O7" s="9">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P7" s="9">
+        <v>5.4820000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -1033,22 +1093,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:25" s="3" customFormat="1">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="12" t="s">
@@ -1097,9 +1157,9 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
+    <row r="2" spans="1:25">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
       <c r="C2" s="12"/>
       <c r="D2" s="11"/>
       <c r="E2" s="4" t="s">
@@ -1142,12 +1202,12 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+    <row r="3" spans="1:25">
+      <c r="A3" s="14">
         <v>46034</v>
       </c>
-      <c r="B3" s="6">
-        <v>46034</v>
+      <c r="B3" s="14">
+        <v>46048</v>
       </c>
       <c r="C3" s="7">
         <v>0.61111111111111105</v>
@@ -1195,12 +1255,12 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+    <row r="4" spans="1:25">
+      <c r="A4" s="14">
         <v>46048</v>
       </c>
-      <c r="B4" s="6">
-        <v>46048</v>
+      <c r="B4" s="14">
+        <v>46055</v>
       </c>
       <c r="C4" s="7">
         <v>0.61111111111111105</v>
@@ -1248,12 +1308,12 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+    <row r="5" spans="1:25">
+      <c r="A5" s="14">
         <v>46055</v>
       </c>
-      <c r="B5" s="6">
-        <v>46055</v>
+      <c r="B5" s="14">
+        <v>46062</v>
       </c>
       <c r="C5" s="7">
         <v>0.61111111111111105</v>
@@ -1289,12 +1349,12 @@
         <v>5.5170000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+    <row r="6" spans="1:25">
+      <c r="A6" s="14">
         <v>46062</v>
       </c>
-      <c r="B6" s="6">
-        <v>46062</v>
+      <c r="B6" s="14">
+        <v>46076</v>
       </c>
       <c r="C6" s="7">
         <v>0.61111111111111105</v>
@@ -1327,6 +1387,47 @@
         <v>4.5</v>
       </c>
       <c r="M6" s="9">
+        <v>5.5170000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" s="14">
+        <v>46076</v>
+      </c>
+      <c r="B7" s="14">
+        <v>46083</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="9">
+        <v>20</v>
+      </c>
+      <c r="F7" s="9">
+        <v>15.5</v>
+      </c>
+      <c r="G7" s="9">
+        <v>17.948</v>
+      </c>
+      <c r="H7" s="9">
+        <v>10.5</v>
+      </c>
+      <c r="I7" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="J7" s="9">
+        <v>8.7479999999999993</v>
+      </c>
+      <c r="K7" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="L7" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="M7" s="9">
         <v>5.5170000000000003</v>
       </c>
     </row>
@@ -1344,24 +1445,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:25" s="3" customFormat="1">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="12" t="s">
@@ -1416,9 +1517,9 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
+    <row r="2" spans="1:25">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
       <c r="C2" s="12"/>
       <c r="D2" s="11"/>
       <c r="E2" s="4" t="s">
@@ -1467,12 +1568,12 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+    <row r="3" spans="1:25">
+      <c r="A3" s="14">
         <v>46034</v>
       </c>
-      <c r="B3" s="6">
-        <v>46034</v>
+      <c r="B3" s="14">
+        <v>46048</v>
       </c>
       <c r="C3" s="7">
         <v>0.61111111111111105</v>
@@ -1526,12 +1627,12 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+    <row r="4" spans="1:25">
+      <c r="A4" s="14">
         <v>46048</v>
       </c>
-      <c r="B4" s="6">
-        <v>46048</v>
+      <c r="B4" s="14">
+        <v>46055</v>
       </c>
       <c r="C4" s="7">
         <v>0.61111111111111105</v>
@@ -1585,12 +1686,12 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+    <row r="5" spans="1:25">
+      <c r="A5" s="14">
         <v>46055</v>
       </c>
-      <c r="B5" s="6">
-        <v>46055</v>
+      <c r="B5" s="14">
+        <v>46062</v>
       </c>
       <c r="C5" s="7">
         <v>0.61111111111111105</v>
@@ -1635,12 +1736,12 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+    <row r="6" spans="1:25">
+      <c r="A6" s="14">
         <v>46062</v>
       </c>
-      <c r="B6" s="6">
-        <v>46062</v>
+      <c r="B6" s="14">
+        <v>46076</v>
       </c>
       <c r="C6" s="7">
         <v>0.61111111111111105</v>
@@ -1683,6 +1784,56 @@
       </c>
       <c r="P6" s="9">
         <v>12.95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" s="14">
+        <v>46076</v>
+      </c>
+      <c r="B7" s="14">
+        <v>46083</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F7" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G7" s="9">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="H7" s="9">
+        <v>5</v>
+      </c>
+      <c r="I7" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="J7" s="9">
+        <v>4.7</v>
+      </c>
+      <c r="K7" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="L7" s="9">
+        <v>6.4</v>
+      </c>
+      <c r="M7" s="9">
+        <v>7.6</v>
+      </c>
+      <c r="N7" s="9">
+        <v>14.9</v>
+      </c>
+      <c r="O7" s="9">
+        <v>12.8</v>
+      </c>
+      <c r="P7" s="9">
+        <v>13.05</v>
       </c>
     </row>
   </sheetData>
@@ -1700,19 +1851,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DFE18-E6A7-46E2-A20D-CA2E453C377B}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="3" customFormat="1">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1765,7 +1916,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="12"/>
@@ -1810,7 +1961,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="6">
         <v>45930</v>
       </c>
@@ -1863,7 +2014,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="E4" s="4"/>
@@ -1888,7 +2039,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
     </row>
@@ -1906,34 +2057,34 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
-  <dimension ref="A1:AJ6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AJ7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.875" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="8.875" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="8.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="8.875" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="8.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="19" width="10" style="9" customWidth="1"/>
-    <col min="20" max="22" width="12.625" style="9" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="14.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="12.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="14.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="28" max="36" width="9" style="9"/>
     <col min="37" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:36" s="3" customFormat="1">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="12" t="s">
@@ -2011,9 +2162,9 @@
       <c r="AI1" s="2"/>
       <c r="AJ1" s="2"/>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
+    <row r="2" spans="1:36">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
       <c r="C2" s="12"/>
       <c r="D2" s="11"/>
       <c r="E2" s="4" t="s">
@@ -2085,11 +2236,11 @@
       <c r="AI2" s="4"/>
       <c r="AJ2" s="4"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+    <row r="3" spans="1:36">
+      <c r="A3" s="14">
         <v>46034</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="14">
         <v>46034</v>
       </c>
       <c r="C3" s="7">
@@ -2161,11 +2312,11 @@
       <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+    <row r="4" spans="1:36">
+      <c r="A4" s="14">
         <v>46052</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="14">
         <v>46052</v>
       </c>
       <c r="C4" s="7">
@@ -2237,11 +2388,11 @@
       <c r="AI4" s="4"/>
       <c r="AJ4" s="4"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+    <row r="5" spans="1:36">
+      <c r="A5" s="14">
         <v>46066</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="14">
         <v>46066</v>
       </c>
       <c r="C5" s="7">
@@ -2296,11 +2447,11 @@
         <v>155.79</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+    <row r="6" spans="1:36">
+      <c r="A6" s="14">
         <v>46079</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="14">
         <v>46079</v>
       </c>
       <c r="C6" s="7">
@@ -2353,6 +2504,11 @@
       </c>
       <c r="V6" s="9">
         <v>167.79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36">
+      <c r="A7" s="14" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2370,14 +2526,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF9DD02-7584-4E7B-8430-E8812C31F69E}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="B1" s="10" t="s">
         <v>61</v>
       </c>
@@ -2385,7 +2541,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="10" t="s">
         <v>8</v>
       </c>
@@ -2396,7 +2552,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="10"/>
       <c r="B3" s="1" t="s">
         <v>11</v>
@@ -2405,7 +2561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="10"/>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -2414,7 +2570,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="10"/>
       <c r="B5" s="1" t="s">
         <v>14</v>
@@ -2423,7 +2579,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="10" t="s">
         <v>16</v>
       </c>
@@ -2432,21 +2588,21 @@
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" s="10"/>
       <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="10"/>
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="10" t="s">
         <v>20</v>
       </c>
@@ -2457,7 +2613,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" s="10"/>
       <c r="B10" s="1" t="s">
         <v>23</v>
@@ -2466,7 +2622,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" s="10"/>
       <c r="B11" s="1" t="s">
         <v>24</v>
@@ -2475,7 +2631,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" s="10" t="s">
         <v>25</v>
       </c>
@@ -2484,28 +2640,28 @@
       </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" s="10"/>
       <c r="B13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" s="10"/>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" s="10"/>
       <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" s="10" t="s">
         <v>30</v>
       </c>
@@ -2514,21 +2670,21 @@
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" s="10"/>
       <c r="B17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" s="10"/>
       <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" s="10" t="s">
         <v>34</v>
       </c>
@@ -2539,7 +2695,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" s="10"/>
       <c r="B20" s="1" t="s">
         <v>37</v>
@@ -2548,7 +2704,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" s="10"/>
       <c r="B21" s="1" t="s">
         <v>35</v>
@@ -2557,7 +2713,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" s="10"/>
       <c r="B22" s="1" t="s">
         <v>35</v>
@@ -2566,7 +2722,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" s="10"/>
       <c r="B23" s="1" t="s">
         <v>35</v>
@@ -2575,7 +2731,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" s="10" t="s">
         <v>42</v>
       </c>
@@ -2584,28 +2740,28 @@
       </c>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" s="10"/>
       <c r="B25" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" s="10"/>
       <c r="B26" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" s="10"/>
       <c r="B27" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" s="10" t="s">
         <v>47</v>
       </c>
@@ -2614,42 +2770,42 @@
       </c>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" s="10"/>
       <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" s="10"/>
       <c r="B30" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" s="10"/>
       <c r="B31" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" s="10"/>
       <c r="B32" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" s="10"/>
       <c r="B33" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" s="10" t="s">
         <v>54</v>
       </c>
@@ -2658,35 +2814,35 @@
       </c>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" s="10"/>
       <c r="B35" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" s="10"/>
       <c r="B36" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" s="10"/>
       <c r="B37" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" s="10"/>
       <c r="B38" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" s="10"/>
       <c r="B39" s="1" t="s">
         <v>60</v>

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/industry/TrendForce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589DD8EC-E972-2E43-88AE-3369978D2416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0027B40B-9C90-4685-8E90-4A74D54A04EA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16960" yWindow="780" windowWidth="19040" windowHeight="20900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16965" yWindow="780" windowWidth="19035" windowHeight="20895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="74">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -290,9 +290,6 @@
   <si>
     <t>PNY</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>`</t>
   </si>
 </sst>
 </file>
@@ -300,23 +297,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -329,7 +326,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -366,7 +363,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -375,43 +372,43 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -689,28 +686,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -759,11 +756,11 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="11"/>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="14"/>
       <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
@@ -810,11 +807,11 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="14">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A3" s="11">
         <v>46034</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="11">
         <v>46048</v>
       </c>
       <c r="C3" s="7">
@@ -869,11 +866,11 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="14">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A4" s="11">
         <v>46048</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="11">
         <v>46055</v>
       </c>
       <c r="C4" s="7">
@@ -928,11 +925,11 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25">
-      <c r="A5" s="14">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A5" s="11">
         <v>46055</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="11">
         <v>46062</v>
       </c>
       <c r="C5" s="7">
@@ -978,11 +975,11 @@
         <v>4.9729999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
-      <c r="A6" s="14">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A6" s="11">
         <v>46062</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="11">
         <v>46076</v>
       </c>
       <c r="C6" s="7">
@@ -1028,11 +1025,11 @@
         <v>5.2450000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
-      <c r="A7" s="14">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A7" s="11">
         <v>46076</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="11">
         <v>46083</v>
       </c>
       <c r="C7" s="7">
@@ -1076,6 +1073,56 @@
       </c>
       <c r="P7" s="9">
         <v>5.4820000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A8" s="11">
+        <v>46083</v>
+      </c>
+      <c r="B8" s="11">
+        <v>46090</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F8" s="9">
+        <v>1.95</v>
+      </c>
+      <c r="G8" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="H8" s="9">
+        <v>2.5</v>
+      </c>
+      <c r="I8" s="9">
+        <v>1.7</v>
+      </c>
+      <c r="J8" s="9">
+        <v>1.8740000000000001</v>
+      </c>
+      <c r="K8" s="9">
+        <v>12</v>
+      </c>
+      <c r="L8" s="9">
+        <v>8.4</v>
+      </c>
+      <c r="M8" s="9">
+        <v>9.35</v>
+      </c>
+      <c r="N8" s="9">
+        <v>7</v>
+      </c>
+      <c r="O8" s="9">
+        <v>5</v>
+      </c>
+      <c r="P8" s="9">
+        <v>5.8179999999999996</v>
       </c>
     </row>
   </sheetData>
@@ -1093,28 +1140,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1157,11 +1204,11 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="11"/>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="14"/>
       <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1202,11 +1249,11 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="14">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A3" s="11">
         <v>46034</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="11">
         <v>46048</v>
       </c>
       <c r="C3" s="7">
@@ -1255,11 +1302,11 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="14">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A4" s="11">
         <v>46048</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="11">
         <v>46055</v>
       </c>
       <c r="C4" s="7">
@@ -1308,11 +1355,11 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25">
-      <c r="A5" s="14">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A5" s="11">
         <v>46055</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="11">
         <v>46062</v>
       </c>
       <c r="C5" s="7">
@@ -1349,11 +1396,11 @@
         <v>5.5170000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
-      <c r="A6" s="14">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A6" s="11">
         <v>46062</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="11">
         <v>46076</v>
       </c>
       <c r="C6" s="7">
@@ -1390,11 +1437,11 @@
         <v>5.5170000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
-      <c r="A7" s="14">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A7" s="11">
         <v>46076</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="11">
         <v>46083</v>
       </c>
       <c r="C7" s="7">
@@ -1429,6 +1476,47 @@
       </c>
       <c r="M7" s="9">
         <v>5.5170000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A8" s="11">
+        <v>46083</v>
+      </c>
+      <c r="B8" s="11">
+        <v>46090</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="9">
+        <v>22</v>
+      </c>
+      <c r="F8" s="9">
+        <v>17</v>
+      </c>
+      <c r="G8" s="9">
+        <v>20.585999999999999</v>
+      </c>
+      <c r="H8" s="9">
+        <v>11</v>
+      </c>
+      <c r="I8" s="9">
+        <v>8</v>
+      </c>
+      <c r="J8" s="9">
+        <v>10.14</v>
+      </c>
+      <c r="K8" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="L8" s="9">
+        <v>5</v>
+      </c>
+      <c r="M8" s="9">
+        <v>6.45</v>
       </c>
     </row>
   </sheetData>
@@ -1445,30 +1533,30 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.125" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1517,11 +1605,11 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="11"/>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="14"/>
       <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1568,11 +1656,11 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="14">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A3" s="11">
         <v>46034</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="11">
         <v>46048</v>
       </c>
       <c r="C3" s="7">
@@ -1627,11 +1715,11 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="14">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A4" s="11">
         <v>46048</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="11">
         <v>46055</v>
       </c>
       <c r="C4" s="7">
@@ -1686,11 +1774,11 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25">
-      <c r="A5" s="14">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A5" s="11">
         <v>46055</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="11">
         <v>46062</v>
       </c>
       <c r="C5" s="7">
@@ -1736,11 +1824,11 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
-      <c r="A6" s="14">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A6" s="11">
         <v>46062</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="11">
         <v>46076</v>
       </c>
       <c r="C6" s="7">
@@ -1786,11 +1874,11 @@
         <v>12.95</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
-      <c r="A7" s="14">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A7" s="11">
         <v>46076</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="11">
         <v>46083</v>
       </c>
       <c r="C7" s="7">
@@ -1833,6 +1921,56 @@
         <v>12.8</v>
       </c>
       <c r="P7" s="9">
+        <v>13.05</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A8" s="11">
+        <v>46083</v>
+      </c>
+      <c r="B8" s="11">
+        <v>46090</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F8" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G8" s="9">
+        <v>2.4649999999999999</v>
+      </c>
+      <c r="H8" s="9">
+        <v>5</v>
+      </c>
+      <c r="I8" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="J8" s="9">
+        <v>4.75</v>
+      </c>
+      <c r="K8" s="9">
+        <v>7.2</v>
+      </c>
+      <c r="L8" s="9">
+        <v>6.4</v>
+      </c>
+      <c r="M8" s="9">
+        <v>6.7249999999999996</v>
+      </c>
+      <c r="N8" s="9">
+        <v>14.9</v>
+      </c>
+      <c r="O8" s="9">
+        <v>12.8</v>
+      </c>
+      <c r="P8" s="9">
         <v>13.05</v>
       </c>
     </row>
@@ -1851,29 +1989,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DFE18-E6A7-46E2-A20D-CA2E453C377B}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.125" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1916,11 +2054,11 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="11"/>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="14"/>
       <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1961,7 +2099,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45930</v>
       </c>
@@ -1969,7 +2107,7 @@
         <v>45953</v>
       </c>
       <c r="C3" s="7">
-        <v>0.75</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>7</v>
@@ -2014,18 +2152,46 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A4" s="6">
+        <v>46042</v>
+      </c>
+      <c r="B4" s="6">
+        <v>46048</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="4">
+        <v>159</v>
+      </c>
+      <c r="F4" s="4">
+        <v>149</v>
+      </c>
+      <c r="G4" s="4">
+        <v>153.9</v>
+      </c>
+      <c r="H4" s="4">
+        <v>100</v>
+      </c>
+      <c r="I4" s="4">
+        <v>94</v>
+      </c>
+      <c r="J4" s="4">
+        <v>97.1</v>
+      </c>
+      <c r="K4" s="4">
+        <v>65</v>
+      </c>
+      <c r="L4" s="4">
+        <v>58.5</v>
+      </c>
+      <c r="M4" s="4">
+        <v>61.3</v>
+      </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
@@ -2039,7 +2205,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
     </row>
@@ -2057,40 +2223,40 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
-  <dimension ref="A1:AJ7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:AJ6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.875" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.875" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="8.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="8.875" style="9" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="8.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="8.875" style="9" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="19" width="10" style="9" customWidth="1"/>
-    <col min="20" max="22" width="12.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="14.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="12.625" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="13.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="14.125" style="9" bestFit="1" customWidth="1"/>
     <col min="28" max="36" width="9" style="9"/>
     <col min="37" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="3" customFormat="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -2162,11 +2328,11 @@
       <c r="AI1" s="2"/>
       <c r="AJ1" s="2"/>
     </row>
-    <row r="2" spans="1:36">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="11"/>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="14"/>
       <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
@@ -2236,11 +2402,11 @@
       <c r="AI2" s="4"/>
       <c r="AJ2" s="4"/>
     </row>
-    <row r="3" spans="1:36">
-      <c r="A3" s="14">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A3" s="11">
         <v>46034</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="11">
         <v>46034</v>
       </c>
       <c r="C3" s="7">
@@ -2312,11 +2478,11 @@
       <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
     </row>
-    <row r="4" spans="1:36">
-      <c r="A4" s="14">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A4" s="11">
         <v>46052</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="11">
         <v>46052</v>
       </c>
       <c r="C4" s="7">
@@ -2388,11 +2554,11 @@
       <c r="AI4" s="4"/>
       <c r="AJ4" s="4"/>
     </row>
-    <row r="5" spans="1:36">
-      <c r="A5" s="14">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A5" s="11">
         <v>46066</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="11">
         <v>46066</v>
       </c>
       <c r="C5" s="7">
@@ -2447,11 +2613,11 @@
         <v>155.79</v>
       </c>
     </row>
-    <row r="6" spans="1:36">
-      <c r="A6" s="14">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A6" s="11">
         <v>46079</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="11">
         <v>46079</v>
       </c>
       <c r="C6" s="7">
@@ -2504,11 +2670,6 @@
       </c>
       <c r="V6" s="9">
         <v>167.79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36">
-      <c r="A7" s="14" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2526,14 +2687,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF9DD02-7584-4E7B-8430-E8812C31F69E}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B1" s="10" t="s">
         <v>61</v>
       </c>
@@ -2541,7 +2702,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>8</v>
       </c>
@@ -2552,7 +2713,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="10"/>
       <c r="B3" s="1" t="s">
         <v>11</v>
@@ -2561,7 +2722,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -2570,7 +2731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
       <c r="B5" s="1" t="s">
         <v>14</v>
@@ -2579,7 +2740,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>16</v>
       </c>
@@ -2588,21 +2749,21 @@
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>20</v>
       </c>
@@ -2613,7 +2774,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
       <c r="B10" s="1" t="s">
         <v>23</v>
@@ -2622,7 +2783,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="10"/>
       <c r="B11" s="1" t="s">
         <v>24</v>
@@ -2631,7 +2792,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>25</v>
       </c>
@@ -2640,28 +2801,28 @@
       </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>30</v>
       </c>
@@ -2670,21 +2831,21 @@
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="10"/>
       <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>34</v>
       </c>
@@ -2695,7 +2856,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="10"/>
       <c r="B20" s="1" t="s">
         <v>37</v>
@@ -2704,7 +2865,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="10"/>
       <c r="B21" s="1" t="s">
         <v>35</v>
@@ -2713,7 +2874,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
       <c r="B22" s="1" t="s">
         <v>35</v>
@@ -2722,7 +2883,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="10"/>
       <c r="B23" s="1" t="s">
         <v>35</v>
@@ -2731,7 +2892,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
         <v>42</v>
       </c>
@@ -2740,28 +2901,28 @@
       </c>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="10"/>
       <c r="B25" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="10"/>
       <c r="B26" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="10"/>
       <c r="B27" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
         <v>47</v>
       </c>
@@ -2770,42 +2931,42 @@
       </c>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="10"/>
       <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
       <c r="B30" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="10"/>
       <c r="B31" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="10"/>
       <c r="B32" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="10"/>
       <c r="B33" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>54</v>
       </c>
@@ -2814,35 +2975,35 @@
       </c>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="10"/>
       <c r="B35" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="10"/>
       <c r="B36" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
       <c r="B37" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="10"/>
       <c r="B38" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="10"/>
       <c r="B39" s="1" t="s">
         <v>60</v>

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0027B40B-9C90-4685-8E90-4A74D54A04EA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A2E668-D785-4BBB-B478-BCCD918523A6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16965" yWindow="780" windowWidth="19035" windowHeight="20895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="74">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -686,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
@@ -1123,6 +1123,56 @@
       </c>
       <c r="P8" s="9">
         <v>5.8179999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A9" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B9" s="11">
+        <v>46097</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="9">
+        <v>3</v>
+      </c>
+      <c r="F9" s="9">
+        <v>2</v>
+      </c>
+      <c r="G9" s="9">
+        <v>2.4670000000000001</v>
+      </c>
+      <c r="H9" s="9">
+        <v>2.6</v>
+      </c>
+      <c r="I9" s="9">
+        <v>1.8</v>
+      </c>
+      <c r="J9" s="9">
+        <v>2.0169999999999999</v>
+      </c>
+      <c r="K9" s="9">
+        <v>14.5</v>
+      </c>
+      <c r="L9" s="9">
+        <v>9</v>
+      </c>
+      <c r="M9" s="9">
+        <v>10.275</v>
+      </c>
+      <c r="N9" s="9">
+        <v>7.3</v>
+      </c>
+      <c r="O9" s="9">
+        <v>5.8</v>
+      </c>
+      <c r="P9" s="9">
+        <v>6.2910000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -1140,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
@@ -1517,6 +1567,47 @@
       </c>
       <c r="M8" s="9">
         <v>6.45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A9" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B9" s="11">
+        <v>46097</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="9">
+        <v>25</v>
+      </c>
+      <c r="F9" s="9">
+        <v>18</v>
+      </c>
+      <c r="G9" s="9">
+        <v>23.134</v>
+      </c>
+      <c r="H9" s="9">
+        <v>12</v>
+      </c>
+      <c r="I9" s="9">
+        <v>8.5</v>
+      </c>
+      <c r="J9" s="9">
+        <v>11.24</v>
+      </c>
+      <c r="K9" s="9">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L9" s="9">
+        <v>5</v>
+      </c>
+      <c r="M9" s="9">
+        <v>6.9669999999999996</v>
       </c>
     </row>
   </sheetData>
@@ -1533,7 +1624,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
@@ -1972,6 +2063,56 @@
       </c>
       <c r="P8" s="9">
         <v>13.05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A9" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B9" s="11">
+        <v>46097</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="9">
+        <v>3</v>
+      </c>
+      <c r="F9" s="9">
+        <v>2.5</v>
+      </c>
+      <c r="G9" s="9">
+        <v>2.7749999999999999</v>
+      </c>
+      <c r="H9" s="9">
+        <v>5.7</v>
+      </c>
+      <c r="I9" s="9">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J9" s="9">
+        <v>5.25</v>
+      </c>
+      <c r="K9" s="9">
+        <v>8</v>
+      </c>
+      <c r="L9" s="9">
+        <v>6.85</v>
+      </c>
+      <c r="M9" s="9">
+        <v>7.55</v>
+      </c>
+      <c r="N9" s="9">
+        <v>16</v>
+      </c>
+      <c r="O9" s="9">
+        <v>13.8</v>
+      </c>
+      <c r="P9" s="9">
+        <v>15.1</v>
       </c>
     </row>
   </sheetData>
@@ -2223,15 +2364,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AJ7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="8.875" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="8.875" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="8.875" style="9" bestFit="1" customWidth="1"/>
@@ -2410,7 +2551,7 @@
         <v>46034</v>
       </c>
       <c r="C3" s="7">
-        <v>0.66666666666666663</v>
+        <v>0.5625</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>7</v>
@@ -2486,7 +2627,7 @@
         <v>46052</v>
       </c>
       <c r="C4" s="7">
-        <v>0.66666666666666663</v>
+        <v>0.5625</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>7</v>
@@ -2562,7 +2703,7 @@
         <v>46066</v>
       </c>
       <c r="C5" s="7">
-        <v>0.66666666666666663</v>
+        <v>0.5625</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>72</v>
@@ -2621,7 +2762,7 @@
         <v>46079</v>
       </c>
       <c r="C6" s="7">
-        <v>0.66666666666666663</v>
+        <v>0.5625</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>72</v>
@@ -2670,6 +2811,65 @@
       </c>
       <c r="V6" s="9">
         <v>167.79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A7" s="11">
+        <v>46097</v>
+      </c>
+      <c r="B7" s="11">
+        <v>46097</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0.5625</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="9">
+        <v>84.99</v>
+      </c>
+      <c r="F7" s="9">
+        <v>84.99</v>
+      </c>
+      <c r="G7" s="9">
+        <v>84.99</v>
+      </c>
+      <c r="H7" s="9">
+        <v>152.6</v>
+      </c>
+      <c r="I7" s="9">
+        <v>117.5</v>
+      </c>
+      <c r="J7" s="9">
+        <v>135</v>
+      </c>
+      <c r="K7" s="9">
+        <v>199.99</v>
+      </c>
+      <c r="L7" s="9">
+        <v>199.99</v>
+      </c>
+      <c r="M7" s="9">
+        <v>199.99</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>289.99</v>
+      </c>
+      <c r="R7" s="9">
+        <v>289.99</v>
+      </c>
+      <c r="S7" s="9">
+        <v>289.99</v>
+      </c>
+      <c r="T7" s="9">
+        <v>179.79</v>
+      </c>
+      <c r="U7" s="9">
+        <v>131.97</v>
+      </c>
+      <c r="V7" s="9">
+        <v>155.88</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A2E668-D785-4BBB-B478-BCCD918523A6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8540DC78-7A2D-428D-9CC7-A564E72BD7C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16965" yWindow="780" windowWidth="19035" windowHeight="20895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
-    <sheet name="Wafer" sheetId="3" r:id="rId2"/>
-    <sheet name="Memory Card" sheetId="4" r:id="rId3"/>
-    <sheet name="PC-Client OEM SSD" sheetId="5" r:id="rId4"/>
-    <sheet name="SSD Street" sheetId="6" r:id="rId5"/>
-    <sheet name="info" sheetId="2" r:id="rId6"/>
+    <sheet name="Flash Contract" sheetId="7" r:id="rId2"/>
+    <sheet name="Wafer" sheetId="3" r:id="rId3"/>
+    <sheet name="Memory Card" sheetId="4" r:id="rId4"/>
+    <sheet name="PC-Client OEM SSD" sheetId="5" r:id="rId5"/>
+    <sheet name="SSD Street" sheetId="6" r:id="rId6"/>
+    <sheet name="fig" sheetId="8" r:id="rId7"/>
+    <sheet name="info" sheetId="2" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="74">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -421,6 +423,1235 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Flash!$G$1:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> SLC 2Gb 256MBx8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Flash!$B$3:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46104</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Flash!$G$3:$G$10</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1.722</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.9670000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.1890000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.4670000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.7330000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6B79-40DA-9EC1-A7F6F9328776}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Flash!$J$1:$J$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> SLC 1Gb 128MBx8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Flash!$B$3:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46104</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Flash!$J$3:$J$10</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1.43</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.623</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.673</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7490000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.8180000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.8740000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.0169999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.2650000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6B79-40DA-9EC1-A7F6F9328776}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Flash!$M$1:$M$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> MLC 64Gb 8GBx8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Flash!$B$3:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46104</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Flash!$M$3:$M$10</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>7.1630000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.375</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.875</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10.275</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-6B79-40DA-9EC1-A7F6F9328776}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Flash!$P$1:$P$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> MLC 32Gb 4GBx8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Flash!$B$3:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46104</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Flash!$P$3:$P$10</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>4.4050000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.9050000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.9729999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.2450000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.4820000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.8179999999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.2910000000000004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.9329999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-6B79-40DA-9EC1-A7F6F9328776}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1736742112"/>
+        <c:axId val="1734594464"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1736742112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46387"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy/mm;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1734594464"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="2"/>
+        <c:majorTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1734594464"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0_);[Red]\(#,##0\)" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1736742112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A090495-C8A6-4531-B130-EA41833C1A21}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -686,7 +1917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
@@ -1173,6 +2404,56 @@
       </c>
       <c r="P9" s="9">
         <v>6.2910000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A10" s="11">
+        <v>46097</v>
+      </c>
+      <c r="B10" s="11">
+        <v>46104</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="9">
+        <v>3.3</v>
+      </c>
+      <c r="F10" s="9">
+        <v>2.35</v>
+      </c>
+      <c r="G10" s="9">
+        <v>2.7330000000000001</v>
+      </c>
+      <c r="H10" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="I10" s="9">
+        <v>2</v>
+      </c>
+      <c r="J10" s="9">
+        <v>2.2650000000000001</v>
+      </c>
+      <c r="K10" s="9">
+        <v>15</v>
+      </c>
+      <c r="L10" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="M10" s="9">
+        <v>11.5</v>
+      </c>
+      <c r="N10" s="9">
+        <v>8</v>
+      </c>
+      <c r="O10" s="9">
+        <v>6</v>
+      </c>
+      <c r="P10" s="9">
+        <v>6.9329999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -1189,8 +2470,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6DA72B-EEC5-42C3-B327-5A9F9ACABB0A}">
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
@@ -1215,31 +2496,31 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -1301,43 +2582,37 @@
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
-        <v>46034</v>
+        <v>46022</v>
       </c>
       <c r="B3" s="11">
-        <v>46048</v>
+        <v>46052</v>
       </c>
       <c r="C3" s="7">
-        <v>0.61111111111111105</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="4">
-        <v>15.8</v>
-      </c>
+      <c r="E3" s="4"/>
       <c r="F3" s="4">
-        <v>14</v>
+        <v>3.22</v>
       </c>
       <c r="G3" s="4">
-        <v>15.052</v>
-      </c>
-      <c r="H3" s="4">
-        <v>8</v>
-      </c>
+        <v>3.3260000000000001</v>
+      </c>
+      <c r="H3" s="4"/>
       <c r="I3" s="4">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="J3" s="4">
-        <v>6.968</v>
-      </c>
-      <c r="K3" s="4">
-        <v>6</v>
-      </c>
+        <v>3.3</v>
+      </c>
+      <c r="K3" s="4"/>
       <c r="L3" s="4">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="M3" s="4">
-        <v>4.9870000000000001</v>
+        <v>2.6629999999999998</v>
       </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
@@ -1354,43 +2629,43 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
-        <v>46048</v>
+        <v>46052</v>
       </c>
       <c r="B4" s="11">
-        <v>46055</v>
+        <v>46079</v>
       </c>
       <c r="C4" s="7">
-        <v>0.61111111111111105</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="4">
-        <v>17.5</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="F4" s="4">
-        <v>14.5</v>
+        <v>9.25</v>
       </c>
       <c r="G4" s="4">
-        <v>16.309999999999999</v>
+        <v>9.4580000000000002</v>
       </c>
       <c r="H4" s="4">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="I4" s="4">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J4" s="4">
-        <v>7.5720000000000001</v>
+        <v>7.0229999999999997</v>
       </c>
       <c r="K4" s="4">
-        <v>6</v>
+        <v>6.15</v>
       </c>
       <c r="L4" s="4">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="M4" s="4">
-        <v>4.9870000000000001</v>
+        <v>5.57</v>
       </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
@@ -1404,211 +2679,6 @@
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="11">
-        <v>46055</v>
-      </c>
-      <c r="B5" s="11">
-        <v>46062</v>
-      </c>
-      <c r="C5" s="7">
-        <v>0.61111111111111105</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="9">
-        <v>19.5</v>
-      </c>
-      <c r="F5" s="9">
-        <v>15.5</v>
-      </c>
-      <c r="G5" s="9">
-        <v>17.724</v>
-      </c>
-      <c r="H5" s="9">
-        <v>10.5</v>
-      </c>
-      <c r="I5" s="9">
-        <v>7.5</v>
-      </c>
-      <c r="J5" s="9">
-        <v>8.7479999999999993</v>
-      </c>
-      <c r="K5" s="9">
-        <v>7.5</v>
-      </c>
-      <c r="L5" s="9">
-        <v>4.5</v>
-      </c>
-      <c r="M5" s="9">
-        <v>5.5170000000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A6" s="11">
-        <v>46062</v>
-      </c>
-      <c r="B6" s="11">
-        <v>46076</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0.61111111111111105</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="9">
-        <v>20</v>
-      </c>
-      <c r="F6" s="9">
-        <v>15.5</v>
-      </c>
-      <c r="G6" s="9">
-        <v>17.948</v>
-      </c>
-      <c r="H6" s="9">
-        <v>10.5</v>
-      </c>
-      <c r="I6" s="9">
-        <v>7.5</v>
-      </c>
-      <c r="J6" s="9">
-        <v>8.7479999999999993</v>
-      </c>
-      <c r="K6" s="9">
-        <v>7.5</v>
-      </c>
-      <c r="L6" s="9">
-        <v>4.5</v>
-      </c>
-      <c r="M6" s="9">
-        <v>5.5170000000000003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A7" s="11">
-        <v>46076</v>
-      </c>
-      <c r="B7" s="11">
-        <v>46083</v>
-      </c>
-      <c r="C7" s="7">
-        <v>0.61111111111111105</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" s="9">
-        <v>20</v>
-      </c>
-      <c r="F7" s="9">
-        <v>15.5</v>
-      </c>
-      <c r="G7" s="9">
-        <v>17.948</v>
-      </c>
-      <c r="H7" s="9">
-        <v>10.5</v>
-      </c>
-      <c r="I7" s="9">
-        <v>7.5</v>
-      </c>
-      <c r="J7" s="9">
-        <v>8.7479999999999993</v>
-      </c>
-      <c r="K7" s="9">
-        <v>7.5</v>
-      </c>
-      <c r="L7" s="9">
-        <v>4.5</v>
-      </c>
-      <c r="M7" s="9">
-        <v>5.5170000000000003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A8" s="11">
-        <v>46083</v>
-      </c>
-      <c r="B8" s="11">
-        <v>46090</v>
-      </c>
-      <c r="C8" s="7">
-        <v>0.61111111111111105</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="9">
-        <v>22</v>
-      </c>
-      <c r="F8" s="9">
-        <v>17</v>
-      </c>
-      <c r="G8" s="9">
-        <v>20.585999999999999</v>
-      </c>
-      <c r="H8" s="9">
-        <v>11</v>
-      </c>
-      <c r="I8" s="9">
-        <v>8</v>
-      </c>
-      <c r="J8" s="9">
-        <v>10.14</v>
-      </c>
-      <c r="K8" s="9">
-        <v>9.5</v>
-      </c>
-      <c r="L8" s="9">
-        <v>5</v>
-      </c>
-      <c r="M8" s="9">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A9" s="11">
-        <v>46090</v>
-      </c>
-      <c r="B9" s="11">
-        <v>46097</v>
-      </c>
-      <c r="C9" s="7">
-        <v>0.61111111111111105</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="9">
-        <v>25</v>
-      </c>
-      <c r="F9" s="9">
-        <v>18</v>
-      </c>
-      <c r="G9" s="9">
-        <v>23.134</v>
-      </c>
-      <c r="H9" s="9">
-        <v>12</v>
-      </c>
-      <c r="I9" s="9">
-        <v>8.5</v>
-      </c>
-      <c r="J9" s="9">
-        <v>11.24</v>
-      </c>
-      <c r="K9" s="9">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="L9" s="9">
-        <v>5</v>
-      </c>
-      <c r="M9" s="9">
-        <v>6.9669999999999996</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1623,8 +2693,483 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
+  <dimension ref="A1:Y10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="25" width="9" style="9"/>
+    <col min="26" max="16384" width="9" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A3" s="11">
+        <v>46034</v>
+      </c>
+      <c r="B3" s="11">
+        <v>46048</v>
+      </c>
+      <c r="C3" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="4">
+        <v>15.8</v>
+      </c>
+      <c r="F3" s="4">
+        <v>14</v>
+      </c>
+      <c r="G3" s="4">
+        <v>15.052</v>
+      </c>
+      <c r="H3" s="4">
+        <v>8</v>
+      </c>
+      <c r="I3" s="4">
+        <v>6</v>
+      </c>
+      <c r="J3" s="4">
+        <v>6.968</v>
+      </c>
+      <c r="K3" s="4">
+        <v>6</v>
+      </c>
+      <c r="L3" s="4">
+        <v>4</v>
+      </c>
+      <c r="M3" s="4">
+        <v>4.9870000000000001</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A4" s="11">
+        <v>46048</v>
+      </c>
+      <c r="B4" s="11">
+        <v>46055</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="4">
+        <v>17.5</v>
+      </c>
+      <c r="F4" s="4">
+        <v>14.5</v>
+      </c>
+      <c r="G4" s="4">
+        <v>16.309999999999999</v>
+      </c>
+      <c r="H4" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="I4" s="4">
+        <v>7</v>
+      </c>
+      <c r="J4" s="4">
+        <v>7.5720000000000001</v>
+      </c>
+      <c r="K4" s="4">
+        <v>6</v>
+      </c>
+      <c r="L4" s="4">
+        <v>4</v>
+      </c>
+      <c r="M4" s="4">
+        <v>4.9870000000000001</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A5" s="11">
+        <v>46055</v>
+      </c>
+      <c r="B5" s="11">
+        <v>46062</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="9">
+        <v>19.5</v>
+      </c>
+      <c r="F5" s="9">
+        <v>15.5</v>
+      </c>
+      <c r="G5" s="9">
+        <v>17.724</v>
+      </c>
+      <c r="H5" s="9">
+        <v>10.5</v>
+      </c>
+      <c r="I5" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="J5" s="9">
+        <v>8.7479999999999993</v>
+      </c>
+      <c r="K5" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="L5" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="M5" s="9">
+        <v>5.5170000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A6" s="11">
+        <v>46062</v>
+      </c>
+      <c r="B6" s="11">
+        <v>46076</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="9">
+        <v>20</v>
+      </c>
+      <c r="F6" s="9">
+        <v>15.5</v>
+      </c>
+      <c r="G6" s="9">
+        <v>17.948</v>
+      </c>
+      <c r="H6" s="9">
+        <v>10.5</v>
+      </c>
+      <c r="I6" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="J6" s="9">
+        <v>8.7479999999999993</v>
+      </c>
+      <c r="K6" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="L6" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="M6" s="9">
+        <v>5.5170000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A7" s="11">
+        <v>46076</v>
+      </c>
+      <c r="B7" s="11">
+        <v>46083</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="9">
+        <v>20</v>
+      </c>
+      <c r="F7" s="9">
+        <v>15.5</v>
+      </c>
+      <c r="G7" s="9">
+        <v>17.948</v>
+      </c>
+      <c r="H7" s="9">
+        <v>10.5</v>
+      </c>
+      <c r="I7" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="J7" s="9">
+        <v>8.7479999999999993</v>
+      </c>
+      <c r="K7" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="L7" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="M7" s="9">
+        <v>5.5170000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A8" s="11">
+        <v>46083</v>
+      </c>
+      <c r="B8" s="11">
+        <v>46090</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="9">
+        <v>22</v>
+      </c>
+      <c r="F8" s="9">
+        <v>17</v>
+      </c>
+      <c r="G8" s="9">
+        <v>20.585999999999999</v>
+      </c>
+      <c r="H8" s="9">
+        <v>11</v>
+      </c>
+      <c r="I8" s="9">
+        <v>8</v>
+      </c>
+      <c r="J8" s="9">
+        <v>10.14</v>
+      </c>
+      <c r="K8" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="L8" s="9">
+        <v>5</v>
+      </c>
+      <c r="M8" s="9">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A9" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B9" s="11">
+        <v>46097</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="9">
+        <v>25</v>
+      </c>
+      <c r="F9" s="9">
+        <v>18</v>
+      </c>
+      <c r="G9" s="9">
+        <v>23.134</v>
+      </c>
+      <c r="H9" s="9">
+        <v>12</v>
+      </c>
+      <c r="I9" s="9">
+        <v>8.5</v>
+      </c>
+      <c r="J9" s="9">
+        <v>11.24</v>
+      </c>
+      <c r="K9" s="9">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L9" s="9">
+        <v>5</v>
+      </c>
+      <c r="M9" s="9">
+        <v>6.9669999999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A10" s="11">
+        <v>46097</v>
+      </c>
+      <c r="B10" s="11">
+        <v>46104</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="9">
+        <v>25</v>
+      </c>
+      <c r="F10" s="9">
+        <v>18.5</v>
+      </c>
+      <c r="G10" s="9">
+        <v>23</v>
+      </c>
+      <c r="H10" s="9">
+        <v>12</v>
+      </c>
+      <c r="I10" s="9">
+        <v>8.5</v>
+      </c>
+      <c r="J10" s="9">
+        <v>11.24</v>
+      </c>
+      <c r="K10" s="9">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L10" s="9">
+        <v>5</v>
+      </c>
+      <c r="M10" s="9">
+        <v>6.9669999999999996</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
@@ -2115,6 +3660,56 @@
         <v>15.1</v>
       </c>
     </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A10" s="11">
+        <v>46097</v>
+      </c>
+      <c r="B10" s="11">
+        <v>46104</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="F10" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G10" s="9">
+        <v>3.15</v>
+      </c>
+      <c r="H10" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="I10" s="9">
+        <v>5.8</v>
+      </c>
+      <c r="J10" s="9">
+        <v>6.1</v>
+      </c>
+      <c r="K10" s="9">
+        <v>9.6</v>
+      </c>
+      <c r="L10" s="9">
+        <v>8.6</v>
+      </c>
+      <c r="M10" s="9">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="N10" s="9">
+        <v>19.8</v>
+      </c>
+      <c r="O10" s="9">
+        <v>17.2</v>
+      </c>
+      <c r="P10" s="9">
+        <v>17.95</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -2127,7 +3722,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DFE18-E6A7-46E2-A20D-CA2E453C377B}">
   <dimension ref="A1:Y5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -2362,7 +3957,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
   <dimension ref="A1:AJ7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -2884,7 +4479,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303223D0-B4CB-49AA-99CE-D17D229E45B9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF9DD02-7584-4E7B-8430-E8812C31F69E}">
   <dimension ref="A1:C39"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8540DC78-7A2D-428D-9CC7-A564E72BD7C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65638BC-E754-4A77-A0C0-5BEA57BF8DCE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16965" yWindow="780" windowWidth="19035" windowHeight="20895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16965" yWindow="780" windowWidth="19035" windowHeight="20895" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -476,10 +476,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Flash!$B$3:$B$10</c:f>
+              <c:f>Flash!$B$3:$B$1110</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="1108"/>
                 <c:pt idx="0">
                   <c:v>46048</c:v>
                 </c:pt>
@@ -509,10 +509,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Flash!$G$3:$G$10</c:f>
+              <c:f>Flash!$G$3:$G$1110</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="1108"/>
                 <c:pt idx="0">
                   <c:v>1.722</c:v>
                 </c:pt>
@@ -540,7 +540,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-6B79-40DA-9EC1-A7F6F9328776}"/>
@@ -578,10 +578,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Flash!$B$3:$B$10</c:f>
+              <c:f>Flash!$B$3:$B$1110</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="1108"/>
                 <c:pt idx="0">
                   <c:v>46048</c:v>
                 </c:pt>
@@ -611,10 +611,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Flash!$J$3:$J$10</c:f>
+              <c:f>Flash!$J$3:$J$1110</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="1108"/>
                 <c:pt idx="0">
                   <c:v>1.43</c:v>
                 </c:pt>
@@ -642,7 +642,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-6B79-40DA-9EC1-A7F6F9328776}"/>
@@ -680,10 +680,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Flash!$B$3:$B$10</c:f>
+              <c:f>Flash!$B$3:$B$1110</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="1108"/>
                 <c:pt idx="0">
                   <c:v>46048</c:v>
                 </c:pt>
@@ -713,10 +713,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Flash!$M$3:$M$10</c:f>
+              <c:f>Flash!$M$3:$M$1110</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="1108"/>
                 <c:pt idx="0">
                   <c:v>7.1630000000000003</c:v>
                 </c:pt>
@@ -744,7 +744,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-6B79-40DA-9EC1-A7F6F9328776}"/>
@@ -782,10 +782,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Flash!$B$3:$B$10</c:f>
+              <c:f>Flash!$B$3:$B$1110</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="1108"/>
                 <c:pt idx="0">
                   <c:v>46048</c:v>
                 </c:pt>
@@ -815,10 +815,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Flash!$P$3:$P$10</c:f>
+              <c:f>Flash!$P$3:$P$1110</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="1108"/>
                 <c:pt idx="0">
                   <c:v>4.4050000000000002</c:v>
                 </c:pt>
@@ -846,7 +846,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-6B79-40DA-9EC1-A7F6F9328776}"/>
@@ -1055,6 +1055,1165 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Wafer!$G$1:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>512Gb TLC</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Wafer!$B$3:$B$1110</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="1108"/>
+                <c:pt idx="0">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46104</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Wafer!$G$3:$G$1110</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="1108"/>
+                <c:pt idx="0">
+                  <c:v>15.052</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.309999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.724</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17.948</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17.948</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20.585999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>23.134</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>23</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-127C-4A22-AA4D-5ED48F0636A7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Wafer!$J$1:$J$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>256Gb TLC</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Wafer!$B$3:$B$1110</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="1108"/>
+                <c:pt idx="0">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46104</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Wafer!$J$3:$J$1110</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="1108"/>
+                <c:pt idx="0">
+                  <c:v>6.968</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.5720000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.7479999999999993</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.7479999999999993</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.7479999999999993</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10.14</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11.24</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11.24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-127C-4A22-AA4D-5ED48F0636A7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Wafer!$M$1:$M$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>128Gb TLC</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Wafer!$B$3:$B$1110</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="1108"/>
+                <c:pt idx="0">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46104</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Wafer!$M$3:$M$1110</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="1108"/>
+                <c:pt idx="0">
+                  <c:v>4.9870000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.9870000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5170000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.5170000000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.5170000000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.45</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.9669999999999996</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.9669999999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-127C-4A22-AA4D-5ED48F0636A7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="925360287"/>
+        <c:axId val="336118095"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="925360287"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46387"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy/mm;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="336118095"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="2"/>
+        <c:majorTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="336118095"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0_);[Red]\(#,##0\)" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="925360287"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Memory Card'!$G$1:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>MicroSD 16GB</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Memory Card'!$B$3:$B$1110</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="1108"/>
+                <c:pt idx="0">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46104</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Memory Card'!$G$3:$G$1110</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="1108"/>
+                <c:pt idx="0">
+                  <c:v>2.2149999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.2400000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.35</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.415</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.4500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.4649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.7749999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2C96-4358-81EB-58422B52DC0B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Memory Card'!$J$1:$J$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>MicroSD 32GB</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Memory Card'!$B$3:$B$1110</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="1108"/>
+                <c:pt idx="0">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46104</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Memory Card'!$J$3:$J$1110</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="1108"/>
+                <c:pt idx="0">
+                  <c:v>3.7250000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.2850000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.55</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.75</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2C96-4358-81EB-58422B52DC0B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Memory Card'!$M$1:$M$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>MicroSD 64GB</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Memory Card'!$B$3:$B$1110</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="1108"/>
+                <c:pt idx="0">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46104</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Memory Card'!$M$3:$M$1110</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="1108"/>
+                <c:pt idx="0">
+                  <c:v>5.15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.55</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.7249999999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.55</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.9499999999999993</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-2C96-4358-81EB-58422B52DC0B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Memory Card'!$P$1:$P$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>MicroSD 128GB</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Memory Card'!$B$3:$B$1110</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="1108"/>
+                <c:pt idx="0">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46104</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Memory Card'!$P$3:$P$1110</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="1108"/>
+                <c:pt idx="0">
+                  <c:v>9.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.95</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13.05</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>13.05</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15.1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17.95</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-2C96-4358-81EB-58422B52DC0B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="788227647"/>
+        <c:axId val="803091023"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="788227647"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46387"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy/mm;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="803091023"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="2"/>
+        <c:majorTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="803091023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0_);[Red]\(#,##0\)" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="788227647"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="4"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1095,7 +2254,1119 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1646,6 +3917,82 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="차트 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3026218-40C1-43FD-8738-1BAAD1317A64}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>685799</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>209549</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>676274</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="차트 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F61F409A-CC80-42D2-B56A-BAB2BC986908}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65638BC-E754-4A77-A0C0-5BEA57BF8DCE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED8B264-2AB9-4C18-9992-9C58C6D1CBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16965" yWindow="780" windowWidth="19035" windowHeight="20895" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="74">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -299,23 +299,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -328,7 +328,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -365,7 +365,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -374,34 +374,34 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -409,8 +409,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -428,7 +428,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -504,6 +504,9 @@
                 <c:pt idx="7">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -536,6 +539,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2.7330000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.9889999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -606,6 +612,9 @@
                 <c:pt idx="7">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -638,6 +647,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2.2650000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.4580000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -708,6 +720,9 @@
                 <c:pt idx="7">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -740,6 +755,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12.625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -810,6 +828,9 @@
                 <c:pt idx="7">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -842,6 +863,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>6.9329999999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1015,6 +1039,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1022,7 +1047,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1058,7 +1082,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1134,6 +1158,9 @@
                 <c:pt idx="7">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1166,6 +1193,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>22.834</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1236,6 +1266,9 @@
                 <c:pt idx="7">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1267,6 +1300,9 @@
                   <c:v>11.24</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>11.24</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>11.24</c:v>
                 </c:pt>
               </c:numCache>
@@ -1338,6 +1374,9 @@
                 <c:pt idx="7">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1369,6 +1408,9 @@
                   <c:v>6.9669999999999996</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>6.9669999999999996</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>6.9669999999999996</c:v>
                 </c:pt>
               </c:numCache>
@@ -1543,6 +1585,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1550,7 +1593,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1586,7 +1628,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1662,6 +1704,9 @@
                 <c:pt idx="7">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1694,6 +1739,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>3.15</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.35</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1764,6 +1812,9 @@
                 <c:pt idx="7">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1796,6 +1847,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1866,6 +1920,9 @@
                 <c:pt idx="7">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1898,6 +1955,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8.9499999999999993</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1968,6 +2028,9 @@
                 <c:pt idx="7">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2000,6 +2063,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>17.95</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18.95</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2174,6 +2240,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2181,7 +2248,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4264,18 +4330,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="3" customFormat="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -4334,7 +4400,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -4385,7 +4451,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="11">
         <v>46034</v>
       </c>
@@ -4444,7 +4510,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="11">
         <v>46048</v>
       </c>
@@ -4503,7 +4569,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="11">
         <v>46055</v>
       </c>
@@ -4553,7 +4619,7 @@
         <v>4.9729999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="11">
         <v>46062</v>
       </c>
@@ -4603,7 +4669,7 @@
         <v>5.2450000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="11">
         <v>46076</v>
       </c>
@@ -4653,7 +4719,7 @@
         <v>5.4820000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="11">
         <v>46083</v>
       </c>
@@ -4703,7 +4769,7 @@
         <v>5.8179999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="11">
         <v>46090</v>
       </c>
@@ -4753,7 +4819,7 @@
         <v>6.2910000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="11">
         <v>46097</v>
       </c>
@@ -4801,6 +4867,56 @@
       </c>
       <c r="P10" s="9">
         <v>6.9329999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" s="11">
+        <v>46104</v>
+      </c>
+      <c r="B11" s="11">
+        <v>46111</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="F11" s="9">
+        <v>2.5</v>
+      </c>
+      <c r="G11" s="9">
+        <v>2.9889999999999999</v>
+      </c>
+      <c r="H11" s="9">
+        <v>3.05</v>
+      </c>
+      <c r="I11" s="9">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J11" s="9">
+        <v>2.4580000000000002</v>
+      </c>
+      <c r="K11" s="9">
+        <v>15</v>
+      </c>
+      <c r="L11" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="M11" s="9">
+        <v>12.625</v>
+      </c>
+      <c r="N11" s="9">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="O11" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="P11" s="9">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -4819,17 +4935,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6DA72B-EEC5-42C3-B327-5A9F9ACABB0A}">
   <dimension ref="A1:Y4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="3" customFormat="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -4882,7 +4998,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -4927,7 +5043,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="11">
         <v>46022</v>
       </c>
@@ -4974,7 +5090,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="11">
         <v>46052</v>
       </c>
@@ -5041,18 +5157,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="3" customFormat="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -5105,7 +5221,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -5150,7 +5266,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="11">
         <v>46034</v>
       </c>
@@ -5203,7 +5319,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="11">
         <v>46048</v>
       </c>
@@ -5256,7 +5372,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="11">
         <v>46055</v>
       </c>
@@ -5297,7 +5413,7 @@
         <v>5.5170000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="11">
         <v>46062</v>
       </c>
@@ -5338,7 +5454,7 @@
         <v>5.5170000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="11">
         <v>46076</v>
       </c>
@@ -5379,7 +5495,7 @@
         <v>5.5170000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="11">
         <v>46083</v>
       </c>
@@ -5420,7 +5536,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="11">
         <v>46090</v>
       </c>
@@ -5461,7 +5577,7 @@
         <v>6.9669999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="11">
         <v>46097</v>
       </c>
@@ -5499,6 +5615,47 @@
         <v>5</v>
       </c>
       <c r="M10" s="9">
+        <v>6.9669999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" s="11">
+        <v>46104</v>
+      </c>
+      <c r="B11" s="11">
+        <v>46111</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="9">
+        <v>25</v>
+      </c>
+      <c r="F11" s="9">
+        <v>18.5</v>
+      </c>
+      <c r="G11" s="9">
+        <v>22.834</v>
+      </c>
+      <c r="H11" s="9">
+        <v>12</v>
+      </c>
+      <c r="I11" s="9">
+        <v>8.5</v>
+      </c>
+      <c r="J11" s="9">
+        <v>11.24</v>
+      </c>
+      <c r="K11" s="9">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L11" s="9">
+        <v>5</v>
+      </c>
+      <c r="M11" s="9">
         <v>6.9669999999999996</v>
       </c>
     </row>
@@ -5516,20 +5673,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="3" customFormat="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -5588,7 +5745,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -5639,7 +5796,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="11">
         <v>46034</v>
       </c>
@@ -5698,7 +5855,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="11">
         <v>46048</v>
       </c>
@@ -5757,7 +5914,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="11">
         <v>46055</v>
       </c>
@@ -5807,7 +5964,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="11">
         <v>46062</v>
       </c>
@@ -5857,7 +6014,7 @@
         <v>12.95</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="11">
         <v>46076</v>
       </c>
@@ -5907,7 +6064,7 @@
         <v>13.05</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="11">
         <v>46083</v>
       </c>
@@ -5957,7 +6114,7 @@
         <v>13.05</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="11">
         <v>46090</v>
       </c>
@@ -6007,7 +6164,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="11">
         <v>46097</v>
       </c>
@@ -6055,6 +6212,56 @@
       </c>
       <c r="P10" s="9">
         <v>17.95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" s="11">
+        <v>46104</v>
+      </c>
+      <c r="B11" s="11">
+        <v>46111</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="9">
+        <v>3.8</v>
+      </c>
+      <c r="F11" s="9">
+        <v>3</v>
+      </c>
+      <c r="G11" s="9">
+        <v>3.35</v>
+      </c>
+      <c r="H11" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="I11" s="9">
+        <v>6</v>
+      </c>
+      <c r="J11" s="9">
+        <v>6.4</v>
+      </c>
+      <c r="K11" s="9">
+        <v>10</v>
+      </c>
+      <c r="L11" s="9">
+        <v>9</v>
+      </c>
+      <c r="M11" s="9">
+        <v>9.375</v>
+      </c>
+      <c r="N11" s="9">
+        <v>19.8</v>
+      </c>
+      <c r="O11" s="9">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="P11" s="9">
+        <v>18.95</v>
       </c>
     </row>
   </sheetData>
@@ -6072,19 +6279,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DFE18-E6A7-46E2-A20D-CA2E453C377B}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="3" customFormat="1">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -6137,7 +6344,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="13"/>
@@ -6182,7 +6389,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="6">
         <v>45930</v>
       </c>
@@ -6235,7 +6442,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="6">
         <v>46042</v>
       </c>
@@ -6288,7 +6495,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
     </row>
@@ -6306,30 +6513,21 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
-  <dimension ref="A1:AJ7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AJ8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.875" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.875" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="8.875" style="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="8.875" style="9" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="10" style="9" customWidth="1"/>
-    <col min="20" max="22" width="12.625" style="9" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="14.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="22" width="10.36328125" style="9" customWidth="1"/>
+    <col min="23" max="24" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
     <col min="28" max="36" width="9" style="9"/>
     <col min="37" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" s="3" customFormat="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -6411,7 +6609,7 @@
       <c r="AI1" s="2"/>
       <c r="AJ1" s="2"/>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -6485,7 +6683,7 @@
       <c r="AI2" s="4"/>
       <c r="AJ2" s="4"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36">
       <c r="A3" s="11">
         <v>46034</v>
       </c>
@@ -6561,7 +6759,7 @@
       <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36">
       <c r="A4" s="11">
         <v>46052</v>
       </c>
@@ -6637,7 +6835,7 @@
       <c r="AI4" s="4"/>
       <c r="AJ4" s="4"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36">
       <c r="A5" s="11">
         <v>46066</v>
       </c>
@@ -6696,7 +6894,7 @@
         <v>155.79</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36">
       <c r="A6" s="11">
         <v>46079</v>
       </c>
@@ -6755,7 +6953,7 @@
         <v>167.79</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36">
       <c r="A7" s="11">
         <v>46097</v>
       </c>
@@ -6812,6 +7010,65 @@
       </c>
       <c r="V7" s="9">
         <v>155.88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36">
+      <c r="A8" s="11">
+        <v>46108</v>
+      </c>
+      <c r="B8" s="11">
+        <v>46108</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.4375</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="9">
+        <v>84.99</v>
+      </c>
+      <c r="F8" s="9">
+        <v>84.99</v>
+      </c>
+      <c r="G8" s="9">
+        <v>84.99</v>
+      </c>
+      <c r="H8" s="9">
+        <v>152.6</v>
+      </c>
+      <c r="I8" s="9">
+        <v>117.5</v>
+      </c>
+      <c r="J8" s="9">
+        <v>135</v>
+      </c>
+      <c r="K8" s="9">
+        <v>199.99</v>
+      </c>
+      <c r="L8" s="9">
+        <v>199.99</v>
+      </c>
+      <c r="M8" s="9">
+        <v>199.99</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>289.99</v>
+      </c>
+      <c r="R8" s="9">
+        <v>289.99</v>
+      </c>
+      <c r="S8" s="9">
+        <v>289.99</v>
+      </c>
+      <c r="T8" s="9">
+        <v>139.97</v>
+      </c>
+      <c r="U8" s="9">
+        <v>131.97</v>
+      </c>
+      <c r="V8" s="9">
+        <v>135.97</v>
       </c>
     </row>
   </sheetData>
@@ -6829,7 +7086,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303223D0-B4CB-49AA-99CE-D17D229E45B9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6841,14 +7098,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF9DD02-7584-4E7B-8430-E8812C31F69E}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="28.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="B1" s="10" t="s">
         <v>61</v>
       </c>
@@ -6856,7 +7113,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="10" t="s">
         <v>8</v>
       </c>
@@ -6867,7 +7124,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="10"/>
       <c r="B3" s="1" t="s">
         <v>11</v>
@@ -6876,7 +7133,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="10"/>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -6885,7 +7142,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="10"/>
       <c r="B5" s="1" t="s">
         <v>14</v>
@@ -6894,7 +7151,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="10" t="s">
         <v>16</v>
       </c>
@@ -6903,21 +7160,21 @@
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" s="10"/>
       <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="10"/>
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="10" t="s">
         <v>20</v>
       </c>
@@ -6928,7 +7185,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" s="10"/>
       <c r="B10" s="1" t="s">
         <v>23</v>
@@ -6937,7 +7194,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" s="10"/>
       <c r="B11" s="1" t="s">
         <v>24</v>
@@ -6946,7 +7203,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" s="10" t="s">
         <v>25</v>
       </c>
@@ -6955,28 +7212,28 @@
       </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" s="10"/>
       <c r="B13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" s="10"/>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" s="10"/>
       <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" s="10" t="s">
         <v>30</v>
       </c>
@@ -6985,21 +7242,21 @@
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" s="10"/>
       <c r="B17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" s="10"/>
       <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" s="10" t="s">
         <v>34</v>
       </c>
@@ -7010,7 +7267,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" s="10"/>
       <c r="B20" s="1" t="s">
         <v>37</v>
@@ -7019,7 +7276,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" s="10"/>
       <c r="B21" s="1" t="s">
         <v>35</v>
@@ -7028,7 +7285,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" s="10"/>
       <c r="B22" s="1" t="s">
         <v>35</v>
@@ -7037,7 +7294,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" s="10"/>
       <c r="B23" s="1" t="s">
         <v>35</v>
@@ -7046,7 +7303,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" s="10" t="s">
         <v>42</v>
       </c>
@@ -7055,28 +7312,28 @@
       </c>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" s="10"/>
       <c r="B25" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" s="10"/>
       <c r="B26" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" s="10"/>
       <c r="B27" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" s="10" t="s">
         <v>47</v>
       </c>
@@ -7085,42 +7342,42 @@
       </c>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" s="10"/>
       <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" s="10"/>
       <c r="B30" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" s="10"/>
       <c r="B31" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" s="10"/>
       <c r="B32" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" s="10"/>
       <c r="B33" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" s="10" t="s">
         <v>54</v>
       </c>
@@ -7129,35 +7386,35 @@
       </c>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" s="10"/>
       <c r="B35" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" s="10"/>
       <c r="B36" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" s="10"/>
       <c r="B37" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" s="10"/>
       <c r="B38" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" s="10"/>
       <c r="B39" s="1" t="s">
         <v>60</v>

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED8B264-2AB9-4C18-9992-9C58C6D1CBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3AD949C-2198-4473-BB51-8FB88D51F10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="74">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -299,23 +302,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -328,7 +331,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -365,7 +368,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -374,34 +377,34 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -409,8 +412,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -428,7 +431,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -507,6 +510,9 @@
                 <c:pt idx="8">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -542,6 +548,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>2.9889999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.089</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -615,6 +624,9 @@
                 <c:pt idx="8">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -650,6 +662,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>2.4580000000000002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.573</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -723,6 +738,9 @@
                 <c:pt idx="8">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -758,6 +776,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>12.625</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>13.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -831,6 +852,9 @@
                 <c:pt idx="8">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -866,6 +890,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1039,7 +1066,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1047,6 +1073,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1082,7 +1109,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1161,6 +1188,9 @@
                 <c:pt idx="8">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1196,6 +1226,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>22.834</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>22.155000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1269,6 +1302,9 @@
                 <c:pt idx="8">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1304,6 +1340,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>11.24</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10.92</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1377,6 +1416,9 @@
                 <c:pt idx="8">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1412,6 +1454,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>6.9669999999999996</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.8330000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1585,7 +1630,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1593,6 +1637,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1628,7 +1673,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1707,6 +1752,9 @@
                 <c:pt idx="8">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1742,6 +1790,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>3.35</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.3450000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1815,6 +1866,9 @@
                 <c:pt idx="8">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1850,6 +1904,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.35</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1923,6 +1980,9 @@
                 <c:pt idx="8">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1958,6 +2018,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9.375</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.3000000000000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2031,6 +2094,9 @@
                 <c:pt idx="8">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2066,6 +2132,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>18.95</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18.600000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2240,7 +2309,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2248,6 +2316,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4330,18 +4399,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1">
+    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -4400,7 +4469,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -4451,7 +4520,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>46034</v>
       </c>
@@ -4510,7 +4579,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>46048</v>
       </c>
@@ -4569,7 +4638,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <v>46055</v>
       </c>
@@ -4619,7 +4688,7 @@
         <v>4.9729999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>46062</v>
       </c>
@@ -4669,7 +4738,7 @@
         <v>5.2450000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <v>46076</v>
       </c>
@@ -4719,7 +4788,7 @@
         <v>5.4820000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="11">
         <v>46083</v>
       </c>
@@ -4769,7 +4838,7 @@
         <v>5.8179999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>46090</v>
       </c>
@@ -4819,7 +4888,7 @@
         <v>6.2910000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="11">
         <v>46097</v>
       </c>
@@ -4869,7 +4938,7 @@
         <v>6.9329999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <v>46104</v>
       </c>
@@ -4917,6 +4986,56 @@
       </c>
       <c r="P11" s="9">
         <v>7.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A12" s="11">
+        <v>46111</v>
+      </c>
+      <c r="B12" s="11">
+        <v>46118</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="9">
+        <v>3.7</v>
+      </c>
+      <c r="F12" s="9">
+        <v>2.6</v>
+      </c>
+      <c r="G12" s="9">
+        <v>3.089</v>
+      </c>
+      <c r="H12" s="9">
+        <v>3.2</v>
+      </c>
+      <c r="I12" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J12" s="9">
+        <v>2.573</v>
+      </c>
+      <c r="K12" s="9">
+        <v>16</v>
+      </c>
+      <c r="L12" s="9">
+        <v>10</v>
+      </c>
+      <c r="M12" s="9">
+        <v>13.125</v>
+      </c>
+      <c r="N12" s="9">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="O12" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="P12" s="9">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -4934,18 +5053,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6DA72B-EEC5-42C3-B327-5A9F9ACABB0A}">
-  <dimension ref="A1:Y4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1">
+    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -4998,7 +5117,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -5043,7 +5162,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>46022</v>
       </c>
@@ -5090,7 +5209,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>46052</v>
       </c>
@@ -5142,6 +5261,47 @@
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A5" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B5" s="11">
+        <v>46112</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="9">
+        <v>12.75</v>
+      </c>
+      <c r="F5" s="9">
+        <v>12.55</v>
+      </c>
+      <c r="G5" s="9">
+        <v>12.664999999999999</v>
+      </c>
+      <c r="H5" s="9">
+        <v>8.6</v>
+      </c>
+      <c r="I5" s="9">
+        <v>8.4</v>
+      </c>
+      <c r="J5" s="9">
+        <v>8.5129999999999999</v>
+      </c>
+      <c r="K5" s="9">
+        <v>7.3</v>
+      </c>
+      <c r="L5" s="9">
+        <v>6.9</v>
+      </c>
+      <c r="M5" s="9">
+        <v>7.2080000000000002</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5157,18 +5317,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1">
+    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -5221,7 +5381,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -5266,7 +5426,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>46034</v>
       </c>
@@ -5319,7 +5479,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>46048</v>
       </c>
@@ -5372,7 +5532,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <v>46055</v>
       </c>
@@ -5413,7 +5573,7 @@
         <v>5.5170000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>46062</v>
       </c>
@@ -5454,7 +5614,7 @@
         <v>5.5170000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <v>46076</v>
       </c>
@@ -5495,7 +5655,7 @@
         <v>5.5170000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="11">
         <v>46083</v>
       </c>
@@ -5536,7 +5696,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>46090</v>
       </c>
@@ -5577,7 +5737,7 @@
         <v>6.9669999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="11">
         <v>46097</v>
       </c>
@@ -5618,7 +5778,7 @@
         <v>6.9669999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <v>46104</v>
       </c>
@@ -5657,6 +5817,47 @@
       </c>
       <c r="M11" s="9">
         <v>6.9669999999999996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A12" s="11">
+        <v>46111</v>
+      </c>
+      <c r="B12" s="11">
+        <v>46118</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="9">
+        <v>24</v>
+      </c>
+      <c r="F12" s="9">
+        <v>17</v>
+      </c>
+      <c r="G12" s="9">
+        <v>22.155000000000001</v>
+      </c>
+      <c r="H12" s="9">
+        <v>11.8</v>
+      </c>
+      <c r="I12" s="9">
+        <v>8</v>
+      </c>
+      <c r="J12" s="9">
+        <v>10.92</v>
+      </c>
+      <c r="K12" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="L12" s="9">
+        <v>5</v>
+      </c>
+      <c r="M12" s="9">
+        <v>6.8330000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -5673,20 +5874,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.125" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1">
+    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -5745,7 +5946,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -5796,7 +5997,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>46034</v>
       </c>
@@ -5855,7 +6056,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>46048</v>
       </c>
@@ -5914,7 +6115,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <v>46055</v>
       </c>
@@ -5964,7 +6165,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>46062</v>
       </c>
@@ -6014,7 +6215,7 @@
         <v>12.95</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <v>46076</v>
       </c>
@@ -6064,7 +6265,7 @@
         <v>13.05</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="11">
         <v>46083</v>
       </c>
@@ -6114,7 +6315,7 @@
         <v>13.05</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>46090</v>
       </c>
@@ -6164,7 +6365,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="11">
         <v>46097</v>
       </c>
@@ -6214,7 +6415,7 @@
         <v>17.95</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <v>46104</v>
       </c>
@@ -6262,6 +6463,56 @@
       </c>
       <c r="P11" s="9">
         <v>18.95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A12" s="11">
+        <v>46111</v>
+      </c>
+      <c r="B12" s="11">
+        <v>46118</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="9">
+        <v>3.8</v>
+      </c>
+      <c r="F12" s="9">
+        <v>3.1</v>
+      </c>
+      <c r="G12" s="9">
+        <v>3.3450000000000002</v>
+      </c>
+      <c r="H12" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="I12" s="9">
+        <v>6</v>
+      </c>
+      <c r="J12" s="9">
+        <v>6.35</v>
+      </c>
+      <c r="K12" s="9">
+        <v>10</v>
+      </c>
+      <c r="L12" s="9">
+        <v>9</v>
+      </c>
+      <c r="M12" s="9">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="N12" s="9">
+        <v>19.3</v>
+      </c>
+      <c r="O12" s="9">
+        <v>17.8</v>
+      </c>
+      <c r="P12" s="9">
+        <v>18.600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -6279,19 +6530,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DFE18-E6A7-46E2-A20D-CA2E453C377B}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.125" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1">
+    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -6344,7 +6595,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="13"/>
@@ -6389,7 +6640,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45930</v>
       </c>
@@ -6442,7 +6693,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>46042</v>
       </c>
@@ -6495,7 +6746,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
     </row>
@@ -6514,20 +6765,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
   <dimension ref="A1:AJ8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="22" width="10.36328125" style="9" customWidth="1"/>
-    <col min="23" max="24" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="22" width="10.375" style="9" customWidth="1"/>
+    <col min="23" max="24" width="13.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="14.125" style="9" bestFit="1" customWidth="1"/>
     <col min="28" max="36" width="9" style="9"/>
     <col min="37" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="3" customFormat="1">
+    <row r="1" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -6609,7 +6860,7 @@
       <c r="AI1" s="2"/>
       <c r="AJ1" s="2"/>
     </row>
-    <row r="2" spans="1:36">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -6683,7 +6934,7 @@
       <c r="AI2" s="4"/>
       <c r="AJ2" s="4"/>
     </row>
-    <row r="3" spans="1:36">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>46034</v>
       </c>
@@ -6759,7 +7010,7 @@
       <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
     </row>
-    <row r="4" spans="1:36">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>46052</v>
       </c>
@@ -6835,7 +7086,7 @@
       <c r="AI4" s="4"/>
       <c r="AJ4" s="4"/>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <v>46066</v>
       </c>
@@ -6894,7 +7145,7 @@
         <v>155.79</v>
       </c>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>46079</v>
       </c>
@@ -6953,7 +7204,7 @@
         <v>167.79</v>
       </c>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <v>46097</v>
       </c>
@@ -7012,7 +7263,7 @@
         <v>155.88</v>
       </c>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A8" s="11">
         <v>46108</v>
       </c>
@@ -7086,7 +7337,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303223D0-B4CB-49AA-99CE-D17D229E45B9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7098,14 +7349,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF9DD02-7584-4E7B-8430-E8812C31F69E}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B1" s="10" t="s">
         <v>61</v>
       </c>
@@ -7113,7 +7364,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>8</v>
       </c>
@@ -7124,7 +7375,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="10"/>
       <c r="B3" s="1" t="s">
         <v>11</v>
@@ -7133,7 +7384,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -7142,7 +7393,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
       <c r="B5" s="1" t="s">
         <v>14</v>
@@ -7151,7 +7402,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>16</v>
       </c>
@@ -7160,21 +7411,21 @@
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>20</v>
       </c>
@@ -7185,7 +7436,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
       <c r="B10" s="1" t="s">
         <v>23</v>
@@ -7194,7 +7445,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="10"/>
       <c r="B11" s="1" t="s">
         <v>24</v>
@@ -7203,7 +7454,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>25</v>
       </c>
@@ -7212,28 +7463,28 @@
       </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>30</v>
       </c>
@@ -7242,21 +7493,21 @@
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="10"/>
       <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>34</v>
       </c>
@@ -7267,7 +7518,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="10"/>
       <c r="B20" s="1" t="s">
         <v>37</v>
@@ -7276,7 +7527,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="10"/>
       <c r="B21" s="1" t="s">
         <v>35</v>
@@ -7285,7 +7536,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
       <c r="B22" s="1" t="s">
         <v>35</v>
@@ -7294,7 +7545,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="10"/>
       <c r="B23" s="1" t="s">
         <v>35</v>
@@ -7303,7 +7554,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
         <v>42</v>
       </c>
@@ -7312,28 +7563,28 @@
       </c>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="10"/>
       <c r="B25" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="10"/>
       <c r="B26" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="10"/>
       <c r="B27" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
         <v>47</v>
       </c>
@@ -7342,42 +7593,42 @@
       </c>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="10"/>
       <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
       <c r="B30" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="10"/>
       <c r="B31" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="10"/>
       <c r="B32" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="10"/>
       <c r="B33" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>54</v>
       </c>
@@ -7386,35 +7637,35 @@
       </c>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="10"/>
       <c r="B35" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="10"/>
       <c r="B36" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
       <c r="B37" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="10"/>
       <c r="B38" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="10"/>
       <c r="B39" s="1" t="s">
         <v>60</v>

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3AD949C-2198-4473-BB51-8FB88D51F10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF55DC8-FE48-447E-A7A2-B02828E45AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -27,15 +27,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="74">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -513,6 +510,9 @@
                 <c:pt idx="9">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -551,6 +551,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>3.089</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -627,6 +630,9 @@
                 <c:pt idx="9">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -665,6 +671,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>2.573</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.8650000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -741,6 +750,9 @@
                 <c:pt idx="9">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -779,6 +791,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>13.125</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -855,6 +870,9 @@
                 <c:pt idx="9">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -893,6 +911,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.6669999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1066,6 +1087,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1073,7 +1095,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1191,6 +1212,9 @@
                 <c:pt idx="9">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1229,6 +1253,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>22.155000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>21.678999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1305,6 +1332,9 @@
                 <c:pt idx="9">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1342,6 +1372,9 @@
                   <c:v>11.24</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>10.92</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>10.92</c:v>
                 </c:pt>
               </c:numCache>
@@ -1419,6 +1452,9 @@
                 <c:pt idx="9">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1456,6 +1492,9 @@
                   <c:v>6.9669999999999996</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>6.8330000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>6.8330000000000002</c:v>
                 </c:pt>
               </c:numCache>
@@ -1630,6 +1669,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1637,7 +1677,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1755,6 +1794,9 @@
                 <c:pt idx="9">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1793,6 +1835,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>3.3450000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.34</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1869,6 +1914,9 @@
                 <c:pt idx="9">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1907,6 +1955,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>6.35</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.3250000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1983,6 +2034,9 @@
                 <c:pt idx="9">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2021,6 +2075,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>9.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.2750000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2097,6 +2154,9 @@
                 <c:pt idx="9">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2135,6 +2195,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>18.600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>18.55</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2309,6 +2372,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2316,7 +2380,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4399,13 +4462,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -5036,6 +5099,56 @@
       </c>
       <c r="P12" s="9">
         <v>7.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A13" s="11">
+        <v>46118</v>
+      </c>
+      <c r="B13" s="11">
+        <v>46125</v>
+      </c>
+      <c r="C13" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="9">
+        <v>4.2</v>
+      </c>
+      <c r="F13" s="9">
+        <v>3</v>
+      </c>
+      <c r="G13" s="9">
+        <v>3.411</v>
+      </c>
+      <c r="H13" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="I13" s="9">
+        <v>2.5</v>
+      </c>
+      <c r="J13" s="9">
+        <v>2.8650000000000002</v>
+      </c>
+      <c r="K13" s="9">
+        <v>20</v>
+      </c>
+      <c r="L13" s="9">
+        <v>12</v>
+      </c>
+      <c r="M13" s="9">
+        <v>15</v>
+      </c>
+      <c r="N13" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="O13" s="9">
+        <v>8</v>
+      </c>
+      <c r="P13" s="9">
+        <v>8.6669999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -5054,12 +5167,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6DA72B-EEC5-42C3-B327-5A9F9ACABB0A}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.19921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -5317,13 +5430,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -5857,6 +5970,47 @@
         <v>5</v>
       </c>
       <c r="M12" s="9">
+        <v>6.8330000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A13" s="11">
+        <v>46118</v>
+      </c>
+      <c r="B13" s="11">
+        <v>46125</v>
+      </c>
+      <c r="C13" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="9">
+        <v>23.5</v>
+      </c>
+      <c r="F13" s="9">
+        <v>17</v>
+      </c>
+      <c r="G13" s="9">
+        <v>21.678999999999998</v>
+      </c>
+      <c r="H13" s="9">
+        <v>11.8</v>
+      </c>
+      <c r="I13" s="9">
+        <v>8</v>
+      </c>
+      <c r="J13" s="9">
+        <v>10.92</v>
+      </c>
+      <c r="K13" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="L13" s="9">
+        <v>5</v>
+      </c>
+      <c r="M13" s="9">
         <v>6.8330000000000002</v>
       </c>
     </row>
@@ -5874,15 +6028,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.09765625" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -6513,6 +6667,56 @@
       </c>
       <c r="P12" s="9">
         <v>18.600000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A13" s="11">
+        <v>46118</v>
+      </c>
+      <c r="B13" s="11">
+        <v>46125</v>
+      </c>
+      <c r="C13" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="9">
+        <v>3.8</v>
+      </c>
+      <c r="F13" s="9">
+        <v>3.1</v>
+      </c>
+      <c r="G13" s="9">
+        <v>3.34</v>
+      </c>
+      <c r="H13" s="9">
+        <v>6.8</v>
+      </c>
+      <c r="I13" s="9">
+        <v>6</v>
+      </c>
+      <c r="J13" s="9">
+        <v>6.3250000000000002</v>
+      </c>
+      <c r="K13" s="9">
+        <v>10</v>
+      </c>
+      <c r="L13" s="9">
+        <v>9</v>
+      </c>
+      <c r="M13" s="9">
+        <v>9.2750000000000004</v>
+      </c>
+      <c r="N13" s="9">
+        <v>19.3</v>
+      </c>
+      <c r="O13" s="9">
+        <v>17.8</v>
+      </c>
+      <c r="P13" s="9">
+        <v>18.55</v>
       </c>
     </row>
   </sheetData>
@@ -6530,14 +6734,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DFE18-E6A7-46E2-A20D-CA2E453C377B}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.09765625" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -6765,15 +6969,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
   <dimension ref="A1:AJ8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="22" width="10.375" style="9" customWidth="1"/>
-    <col min="23" max="24" width="13.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="14.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.19921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="22" width="10.3984375" style="9" customWidth="1"/>
+    <col min="23" max="24" width="13.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="14.09765625" style="9" bestFit="1" customWidth="1"/>
     <col min="28" max="36" width="9" style="9"/>
     <col min="37" max="16384" width="9" style="5"/>
   </cols>
@@ -7337,7 +7541,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303223D0-B4CB-49AA-99CE-D17D229E45B9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7349,14 +7553,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF9DD02-7584-4E7B-8430-E8812C31F69E}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="28.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B1" s="10" t="s">
         <v>61</v>
       </c>
@@ -7364,7 +7568,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="10" t="s">
         <v>8</v>
       </c>
@@ -7375,7 +7579,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="10"/>
       <c r="B3" s="1" t="s">
         <v>11</v>
@@ -7384,7 +7588,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="10"/>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -7393,7 +7597,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="10"/>
       <c r="B5" s="1" t="s">
         <v>14</v>
@@ -7402,7 +7606,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
         <v>16</v>
       </c>
@@ -7411,21 +7615,21 @@
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="10"/>
       <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" s="10"/>
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
         <v>20</v>
       </c>
@@ -7436,7 +7640,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" s="10"/>
       <c r="B10" s="1" t="s">
         <v>23</v>
@@ -7445,7 +7649,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" s="10"/>
       <c r="B11" s="1" t="s">
         <v>24</v>
@@ -7454,7 +7658,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" s="10" t="s">
         <v>25</v>
       </c>
@@ -7463,28 +7667,28 @@
       </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" s="10"/>
       <c r="B13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" s="10"/>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" s="10"/>
       <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" s="10" t="s">
         <v>30</v>
       </c>
@@ -7493,21 +7697,21 @@
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" s="10"/>
       <c r="B17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" s="10"/>
       <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" s="10" t="s">
         <v>34</v>
       </c>
@@ -7518,7 +7722,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20" s="10"/>
       <c r="B20" s="1" t="s">
         <v>37</v>
@@ -7527,7 +7731,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" s="10"/>
       <c r="B21" s="1" t="s">
         <v>35</v>
@@ -7536,7 +7740,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" s="10"/>
       <c r="B22" s="1" t="s">
         <v>35</v>
@@ -7545,7 +7749,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" s="10"/>
       <c r="B23" s="1" t="s">
         <v>35</v>
@@ -7554,7 +7758,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
         <v>42</v>
       </c>
@@ -7563,28 +7767,28 @@
       </c>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" s="10"/>
       <c r="B25" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" s="10"/>
       <c r="B26" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" s="10"/>
       <c r="B27" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" s="10" t="s">
         <v>47</v>
       </c>
@@ -7593,42 +7797,42 @@
       </c>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" s="10"/>
       <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" s="10"/>
       <c r="B30" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31" s="10"/>
       <c r="B31" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32" s="10"/>
       <c r="B32" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A33" s="10"/>
       <c r="B33" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A34" s="10" t="s">
         <v>54</v>
       </c>
@@ -7637,35 +7841,35 @@
       </c>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" s="10"/>
       <c r="B35" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A36" s="10"/>
       <c r="B36" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A37" s="10"/>
       <c r="B37" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A38" s="10"/>
       <c r="B38" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A39" s="10"/>
       <c r="B39" s="1" t="s">
         <v>60</v>

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF55DC8-FE48-447E-A7A2-B02828E45AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D443608-35B2-4FC7-993E-2C298A6705C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="74">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -513,6 +513,9 @@
                 <c:pt idx="10">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -554,6 +557,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>3.411</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.6779999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -633,6 +639,9 @@
                 <c:pt idx="10">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -674,6 +683,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.8650000000000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -753,6 +765,9 @@
                 <c:pt idx="10">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -794,6 +809,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>16.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -873,6 +891,9 @@
                 <c:pt idx="10">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -914,6 +935,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>8.6669999999999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.3670000000000009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1215,6 +1239,9 @@
                 <c:pt idx="10">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1256,6 +1283,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>21.678999999999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>21</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1335,6 +1365,9 @@
                 <c:pt idx="10">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1376,6 +1409,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>10.92</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10.492000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1455,6 +1491,9 @@
                 <c:pt idx="10">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1496,6 +1535,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>6.8330000000000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1797,6 +1839,9 @@
                 <c:pt idx="10">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1837,6 +1882,9 @@
                   <c:v>3.3450000000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>3.34</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>3.34</c:v>
                 </c:pt>
               </c:numCache>
@@ -1917,6 +1965,9 @@
                 <c:pt idx="10">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1958,6 +2009,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>6.3250000000000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2037,6 +2091,9 @@
                 <c:pt idx="10">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2078,6 +2135,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>9.2750000000000004</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.1750000000000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2157,6 +2217,9 @@
                 <c:pt idx="10">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2198,6 +2261,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>18.55</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>18.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4462,7 +4528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y13"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
@@ -5149,6 +5215,56 @@
       </c>
       <c r="P13" s="9">
         <v>8.6669999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A14" s="11">
+        <v>46125</v>
+      </c>
+      <c r="B14" s="11">
+        <v>46132</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="9">
+        <v>4.2</v>
+      </c>
+      <c r="F14" s="9">
+        <v>3.3</v>
+      </c>
+      <c r="G14" s="9">
+        <v>3.6779999999999999</v>
+      </c>
+      <c r="H14" s="9">
+        <v>4</v>
+      </c>
+      <c r="I14" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="J14" s="9">
+        <v>3.125</v>
+      </c>
+      <c r="K14" s="9">
+        <v>22</v>
+      </c>
+      <c r="L14" s="9">
+        <v>12</v>
+      </c>
+      <c r="M14" s="9">
+        <v>16.5</v>
+      </c>
+      <c r="N14" s="9">
+        <v>10</v>
+      </c>
+      <c r="O14" s="9">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="P14" s="9">
+        <v>9.3670000000000009</v>
       </c>
     </row>
   </sheetData>
@@ -5430,7 +5546,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y13"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
@@ -6012,6 +6128,47 @@
       </c>
       <c r="M13" s="9">
         <v>6.8330000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A14" s="11">
+        <v>46125</v>
+      </c>
+      <c r="B14" s="11">
+        <v>46132</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="9">
+        <v>22</v>
+      </c>
+      <c r="F14" s="9">
+        <v>16.5</v>
+      </c>
+      <c r="G14" s="9">
+        <v>21</v>
+      </c>
+      <c r="H14" s="9">
+        <v>11.5</v>
+      </c>
+      <c r="I14" s="9">
+        <v>8</v>
+      </c>
+      <c r="J14" s="9">
+        <v>10.492000000000001</v>
+      </c>
+      <c r="K14" s="9">
+        <v>9</v>
+      </c>
+      <c r="L14" s="9">
+        <v>4.8</v>
+      </c>
+      <c r="M14" s="9">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -6028,7 +6185,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y13"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
@@ -6717,6 +6874,56 @@
       </c>
       <c r="P13" s="9">
         <v>18.55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A14" s="11">
+        <v>46125</v>
+      </c>
+      <c r="B14" s="11">
+        <v>46132</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="9">
+        <v>3.8</v>
+      </c>
+      <c r="F14" s="9">
+        <v>3.1</v>
+      </c>
+      <c r="G14" s="9">
+        <v>3.34</v>
+      </c>
+      <c r="H14" s="9">
+        <v>6.7</v>
+      </c>
+      <c r="I14" s="9">
+        <v>5.7</v>
+      </c>
+      <c r="J14" s="9">
+        <v>6.2</v>
+      </c>
+      <c r="K14" s="9">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L14" s="9">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="M14" s="9">
+        <v>9.1750000000000007</v>
+      </c>
+      <c r="N14" s="9">
+        <v>19</v>
+      </c>
+      <c r="O14" s="9">
+        <v>17</v>
+      </c>
+      <c r="P14" s="9">
+        <v>18.25</v>
       </c>
     </row>
   </sheetData>
@@ -6968,7 +7175,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
-  <dimension ref="A1:AJ8"/>
+  <dimension ref="A1:AJ9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
@@ -7524,6 +7731,65 @@
       </c>
       <c r="V8" s="9">
         <v>135.97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A9" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B9" s="11">
+        <v>46129</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="9">
+        <v>125.54</v>
+      </c>
+      <c r="F9" s="9">
+        <v>124.61</v>
+      </c>
+      <c r="G9" s="9">
+        <v>125.08</v>
+      </c>
+      <c r="H9" s="9">
+        <v>152.6</v>
+      </c>
+      <c r="I9" s="9">
+        <v>117.5</v>
+      </c>
+      <c r="J9" s="9">
+        <v>135</v>
+      </c>
+      <c r="K9" s="9">
+        <v>319.99</v>
+      </c>
+      <c r="L9" s="9">
+        <v>249.99</v>
+      </c>
+      <c r="M9" s="9">
+        <v>284.99</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>399.99</v>
+      </c>
+      <c r="R9" s="9">
+        <v>399.99</v>
+      </c>
+      <c r="S9" s="9">
+        <v>399.99</v>
+      </c>
+      <c r="T9" s="9">
+        <v>154.97</v>
+      </c>
+      <c r="U9" s="9">
+        <v>154.97</v>
+      </c>
+      <c r="V9" s="9">
+        <v>154.97</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D443608-35B2-4FC7-993E-2C298A6705C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714352C3-FCE6-461F-ABB0-98DBB8D2CFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="74">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -516,6 +516,9 @@
                 <c:pt idx="11">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -560,6 +563,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>3.6779999999999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -642,6 +648,9 @@
                 <c:pt idx="11">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -686,6 +695,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>3.125</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -768,6 +780,9 @@
                 <c:pt idx="11">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -812,6 +827,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -894,6 +912,9 @@
                 <c:pt idx="11">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -938,6 +959,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>9.3670000000000009</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9.8000000000000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1242,6 +1266,9 @@
                 <c:pt idx="11">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1286,6 +1313,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>20.972000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1368,6 +1398,9 @@
                 <c:pt idx="11">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1412,6 +1445,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>10.492000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10.476000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1494,6 +1530,9 @@
                 <c:pt idx="11">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1538,6 +1577,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>6.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.58</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1842,6 +1884,9 @@
                 <c:pt idx="11">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1886,6 +1931,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>3.34</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.3250000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1968,6 +2016,9 @@
                 <c:pt idx="11">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2012,6 +2063,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.0250000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2094,6 +2148,9 @@
                 <c:pt idx="11">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2138,6 +2195,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>9.1750000000000007</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.9499999999999993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2220,6 +2280,9 @@
                 <c:pt idx="11">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2264,6 +2327,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>18.25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17.55</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4528,7 +4594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
@@ -5265,6 +5331,56 @@
       </c>
       <c r="P14" s="9">
         <v>9.3670000000000009</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A15" s="11">
+        <v>46132</v>
+      </c>
+      <c r="B15" s="11">
+        <v>46139</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="9">
+        <v>4.3</v>
+      </c>
+      <c r="F15" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="G15" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="H15" s="9">
+        <v>4</v>
+      </c>
+      <c r="I15" s="9">
+        <v>3</v>
+      </c>
+      <c r="J15" s="9">
+        <v>3.4</v>
+      </c>
+      <c r="K15" s="9">
+        <v>25</v>
+      </c>
+      <c r="L15" s="9">
+        <v>14</v>
+      </c>
+      <c r="M15" s="9">
+        <v>17.75</v>
+      </c>
+      <c r="N15" s="9">
+        <v>12</v>
+      </c>
+      <c r="O15" s="9">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="P15" s="9">
+        <v>9.8000000000000007</v>
       </c>
     </row>
   </sheetData>
@@ -5546,7 +5662,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
@@ -6169,6 +6285,47 @@
       </c>
       <c r="M14" s="9">
         <v>6.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A15" s="11">
+        <v>46132</v>
+      </c>
+      <c r="B15" s="11">
+        <v>46139</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="9">
+        <v>21.8</v>
+      </c>
+      <c r="F15" s="9">
+        <v>16.5</v>
+      </c>
+      <c r="G15" s="9">
+        <v>20.972000000000001</v>
+      </c>
+      <c r="H15" s="9">
+        <v>11.5</v>
+      </c>
+      <c r="I15" s="9">
+        <v>8</v>
+      </c>
+      <c r="J15" s="9">
+        <v>10.476000000000001</v>
+      </c>
+      <c r="K15" s="9">
+        <v>9</v>
+      </c>
+      <c r="L15" s="9">
+        <v>4.8</v>
+      </c>
+      <c r="M15" s="9">
+        <v>6.58</v>
       </c>
     </row>
   </sheetData>
@@ -6185,7 +6342,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
@@ -6924,6 +7081,56 @@
       </c>
       <c r="P14" s="9">
         <v>18.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A15" s="11">
+        <v>46132</v>
+      </c>
+      <c r="B15" s="11">
+        <v>46139</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="9">
+        <v>3.7</v>
+      </c>
+      <c r="F15" s="9">
+        <v>3.1</v>
+      </c>
+      <c r="G15" s="9">
+        <v>3.3250000000000002</v>
+      </c>
+      <c r="H15" s="9">
+        <v>6.4</v>
+      </c>
+      <c r="I15" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="J15" s="9">
+        <v>6.0250000000000004</v>
+      </c>
+      <c r="K15" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="L15" s="9">
+        <v>8.4</v>
+      </c>
+      <c r="M15" s="9">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="N15" s="9">
+        <v>18.5</v>
+      </c>
+      <c r="O15" s="9">
+        <v>16.2</v>
+      </c>
+      <c r="P15" s="9">
+        <v>17.55</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215FCBFB-884E-41B3-B8B4-655F02CE3240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12EFB80C-E6B0-4536-B229-24E19E2B89CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="74">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -299,23 +299,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -328,7 +328,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -365,7 +365,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -374,34 +374,34 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -525,6 +525,9 @@
                 <c:pt idx="14">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -578,6 +581,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>3.75</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.7250000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -669,6 +675,9 @@
                 <c:pt idx="14">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -722,6 +731,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>3.45</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.4249999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -813,6 +825,9 @@
                 <c:pt idx="14">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -866,6 +881,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>19.625</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>20.295000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -957,6 +975,9 @@
                 <c:pt idx="14">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1010,6 +1031,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>10.467000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>10.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1323,6 +1347,9 @@
                 <c:pt idx="14">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1376,6 +1403,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>20.472000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>20.541</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1467,6 +1497,9 @@
                 <c:pt idx="14">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1519,6 +1552,9 @@
                   <c:v>10.476000000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>10.476000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>10.476000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -1611,6 +1647,9 @@
                 <c:pt idx="14">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1663,6 +1702,9 @@
                   <c:v>6.58</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>6.58</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>6.58</c:v>
                 </c:pt>
               </c:numCache>
@@ -1977,6 +2019,9 @@
                 <c:pt idx="14">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2030,6 +2075,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>3.15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2121,6 +2169,9 @@
                 <c:pt idx="14">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2174,6 +2225,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>5.6</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2265,6 +2319,9 @@
                 <c:pt idx="14">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2318,6 +2375,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>8.1750000000000007</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2409,6 +2469,9 @@
                 <c:pt idx="14">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2462,6 +2525,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>16.2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15.85</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4726,18 +4792,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="3" customFormat="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -4796,7 +4862,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -4847,7 +4913,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="11">
         <v>46034</v>
       </c>
@@ -4906,7 +4972,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="11">
         <v>46048</v>
       </c>
@@ -4965,7 +5031,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="11">
         <v>46055</v>
       </c>
@@ -5015,7 +5081,7 @@
         <v>4.9729999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="11">
         <v>46062</v>
       </c>
@@ -5065,7 +5131,7 @@
         <v>5.2450000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="11">
         <v>46076</v>
       </c>
@@ -5115,7 +5181,7 @@
         <v>5.4820000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="11">
         <v>46083</v>
       </c>
@@ -5165,7 +5231,7 @@
         <v>5.8179999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="11">
         <v>46090</v>
       </c>
@@ -5215,7 +5281,7 @@
         <v>6.2910000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="11">
         <v>46097</v>
       </c>
@@ -5265,7 +5331,7 @@
         <v>6.9329999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="11">
         <v>46104</v>
       </c>
@@ -5315,7 +5381,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="11">
         <v>46111</v>
       </c>
@@ -5365,7 +5431,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="11">
         <v>46118</v>
       </c>
@@ -5415,7 +5481,7 @@
         <v>8.6669999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="11">
         <v>46125</v>
       </c>
@@ -5465,7 +5531,7 @@
         <v>9.3670000000000009</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="11">
         <v>46132</v>
       </c>
@@ -5515,7 +5581,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="11">
         <v>46139</v>
       </c>
@@ -5565,7 +5631,7 @@
         <v>10.433</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16">
       <c r="A17" s="11">
         <v>46146</v>
       </c>
@@ -5613,6 +5679,56 @@
       </c>
       <c r="P17" s="9">
         <v>10.467000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="11">
+        <v>46153</v>
+      </c>
+      <c r="B18" s="11">
+        <v>46160</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="F18" s="9">
+        <v>3</v>
+      </c>
+      <c r="G18" s="9">
+        <v>3.7250000000000001</v>
+      </c>
+      <c r="H18" s="9">
+        <v>3.8</v>
+      </c>
+      <c r="I18" s="9">
+        <v>3</v>
+      </c>
+      <c r="J18" s="9">
+        <v>3.4249999999999998</v>
+      </c>
+      <c r="K18" s="9">
+        <v>32</v>
+      </c>
+      <c r="L18" s="9">
+        <v>16</v>
+      </c>
+      <c r="M18" s="9">
+        <v>20.295000000000002</v>
+      </c>
+      <c r="N18" s="9">
+        <v>12.3</v>
+      </c>
+      <c r="O18" s="9">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="P18" s="9">
+        <v>10.7</v>
       </c>
     </row>
   </sheetData>
@@ -5631,17 +5747,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6DA72B-EEC5-42C3-B327-5A9F9ACABB0A}">
   <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.19921875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="3" customFormat="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -5694,7 +5810,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -5739,7 +5855,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="11">
         <v>46022</v>
       </c>
@@ -5786,7 +5902,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="11">
         <v>46052</v>
       </c>
@@ -5839,7 +5955,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="11">
         <v>46079</v>
       </c>
@@ -5880,7 +5996,7 @@
         <v>7.2080000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="11">
         <v>46112</v>
       </c>
@@ -5935,18 +6051,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="3" customFormat="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -5999,7 +6115,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -6044,7 +6160,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="11">
         <v>46034</v>
       </c>
@@ -6097,7 +6213,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="11">
         <v>46048</v>
       </c>
@@ -6150,7 +6266,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="11">
         <v>46055</v>
       </c>
@@ -6191,7 +6307,7 @@
         <v>5.5170000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="11">
         <v>46062</v>
       </c>
@@ -6232,7 +6348,7 @@
         <v>5.5170000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="11">
         <v>46076</v>
       </c>
@@ -6273,7 +6389,7 @@
         <v>5.5170000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="11">
         <v>46083</v>
       </c>
@@ -6314,7 +6430,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="11">
         <v>46090</v>
       </c>
@@ -6355,7 +6471,7 @@
         <v>6.9669999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="11">
         <v>46097</v>
       </c>
@@ -6396,7 +6512,7 @@
         <v>6.9669999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="11">
         <v>46104</v>
       </c>
@@ -6437,7 +6553,7 @@
         <v>6.9669999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="11">
         <v>46111</v>
       </c>
@@ -6478,7 +6594,7 @@
         <v>6.8330000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="11">
         <v>46118</v>
       </c>
@@ -6519,7 +6635,7 @@
         <v>6.8330000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="11">
         <v>46125</v>
       </c>
@@ -6560,7 +6676,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="11">
         <v>46132</v>
       </c>
@@ -6601,7 +6717,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="11">
         <v>46139</v>
       </c>
@@ -6642,7 +6758,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13">
       <c r="A17" s="11">
         <v>46146</v>
       </c>
@@ -6680,6 +6796,47 @@
         <v>4.8</v>
       </c>
       <c r="M17" s="9">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="11">
+        <v>46153</v>
+      </c>
+      <c r="B18" s="11">
+        <v>46160</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="9">
+        <v>21.5</v>
+      </c>
+      <c r="F18" s="9">
+        <v>16</v>
+      </c>
+      <c r="G18" s="9">
+        <v>20.541</v>
+      </c>
+      <c r="H18" s="9">
+        <v>11.5</v>
+      </c>
+      <c r="I18" s="9">
+        <v>8</v>
+      </c>
+      <c r="J18" s="9">
+        <v>10.476000000000001</v>
+      </c>
+      <c r="K18" s="9">
+        <v>9</v>
+      </c>
+      <c r="L18" s="9">
+        <v>4.8</v>
+      </c>
+      <c r="M18" s="9">
         <v>6.58</v>
       </c>
     </row>
@@ -6697,20 +6854,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.09765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="3" customFormat="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -6769,7 +6926,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -6820,7 +6977,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="11">
         <v>46034</v>
       </c>
@@ -6879,7 +7036,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="11">
         <v>46048</v>
       </c>
@@ -6938,7 +7095,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="11">
         <v>46055</v>
       </c>
@@ -6988,7 +7145,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="11">
         <v>46062</v>
       </c>
@@ -7038,7 +7195,7 @@
         <v>12.95</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="11">
         <v>46076</v>
       </c>
@@ -7088,7 +7245,7 @@
         <v>13.05</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="11">
         <v>46083</v>
       </c>
@@ -7138,7 +7295,7 @@
         <v>13.05</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="11">
         <v>46090</v>
       </c>
@@ -7188,7 +7345,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="11">
         <v>46097</v>
       </c>
@@ -7238,7 +7395,7 @@
         <v>17.95</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="11">
         <v>46104</v>
       </c>
@@ -7288,7 +7445,7 @@
         <v>18.95</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="11">
         <v>46111</v>
       </c>
@@ -7338,7 +7495,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="11">
         <v>46118</v>
       </c>
@@ -7388,7 +7545,7 @@
         <v>18.55</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="11">
         <v>46125</v>
       </c>
@@ -7438,7 +7595,7 @@
         <v>18.25</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="11">
         <v>46132</v>
       </c>
@@ -7488,7 +7645,7 @@
         <v>17.55</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="11">
         <v>46139</v>
       </c>
@@ -7538,7 +7695,7 @@
         <v>16.649999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16">
       <c r="A17" s="11">
         <v>46146</v>
       </c>
@@ -7586,6 +7743,56 @@
       </c>
       <c r="P17" s="9">
         <v>16.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="11">
+        <v>46153</v>
+      </c>
+      <c r="B18" s="11">
+        <v>46160</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="F18" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G18" s="9">
+        <v>3.1</v>
+      </c>
+      <c r="H18" s="9">
+        <v>6.1</v>
+      </c>
+      <c r="I18" s="9">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J18" s="9">
+        <v>5.4</v>
+      </c>
+      <c r="K18" s="9">
+        <v>8.6</v>
+      </c>
+      <c r="L18" s="9">
+        <v>7</v>
+      </c>
+      <c r="M18" s="9">
+        <v>8</v>
+      </c>
+      <c r="N18" s="9">
+        <v>16.8</v>
+      </c>
+      <c r="O18" s="9">
+        <v>14.5</v>
+      </c>
+      <c r="P18" s="9">
+        <v>15.85</v>
       </c>
     </row>
   </sheetData>
@@ -7603,19 +7810,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DFE18-E6A7-46E2-A20D-CA2E453C377B}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.09765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="3" customFormat="1">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -7668,7 +7875,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="13"/>
@@ -7713,7 +7920,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="6">
         <v>45930</v>
       </c>
@@ -7766,7 +7973,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="6">
         <v>46042</v>
       </c>
@@ -7819,7 +8026,7 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
     </row>
@@ -7837,21 +8044,21 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
-  <dimension ref="A1:AJ10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AJ11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.19921875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="22" width="10.3984375" style="9" customWidth="1"/>
-    <col min="23" max="24" width="13.09765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="14.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="22" width="10.44140625" style="9" customWidth="1"/>
+    <col min="23" max="24" width="13.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="14.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="28" max="36" width="9" style="9"/>
     <col min="37" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" s="3" customFormat="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -7933,7 +8140,7 @@
       <c r="AI1" s="2"/>
       <c r="AJ1" s="2"/>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -8007,7 +8214,7 @@
       <c r="AI2" s="4"/>
       <c r="AJ2" s="4"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36">
       <c r="A3" s="11">
         <v>46034</v>
       </c>
@@ -8083,7 +8290,7 @@
       <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36">
       <c r="A4" s="11">
         <v>46052</v>
       </c>
@@ -8159,7 +8366,7 @@
       <c r="AI4" s="4"/>
       <c r="AJ4" s="4"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36">
       <c r="A5" s="11">
         <v>46066</v>
       </c>
@@ -8218,7 +8425,7 @@
         <v>155.79</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36">
       <c r="A6" s="11">
         <v>46079</v>
       </c>
@@ -8277,7 +8484,7 @@
         <v>167.79</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36">
       <c r="A7" s="11">
         <v>46097</v>
       </c>
@@ -8336,7 +8543,7 @@
         <v>155.88</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36">
       <c r="A8" s="11">
         <v>46108</v>
       </c>
@@ -8395,7 +8602,7 @@
         <v>135.97</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36">
       <c r="A9" s="11">
         <v>46129</v>
       </c>
@@ -8454,7 +8661,7 @@
         <v>154.97</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36">
       <c r="A10" s="11">
         <v>46142</v>
       </c>
@@ -8511,6 +8718,65 @@
       </c>
       <c r="V10" s="9">
         <v>158.88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36">
+      <c r="A11" s="11">
+        <v>46157</v>
+      </c>
+      <c r="B11" s="11">
+        <v>46157</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="9">
+        <v>242</v>
+      </c>
+      <c r="F11" s="9">
+        <v>242</v>
+      </c>
+      <c r="G11" s="9">
+        <v>242</v>
+      </c>
+      <c r="H11" s="9">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="I11" s="9">
+        <v>115.7</v>
+      </c>
+      <c r="J11" s="9">
+        <v>133</v>
+      </c>
+      <c r="K11" s="9">
+        <v>288</v>
+      </c>
+      <c r="L11" s="9">
+        <v>249.99</v>
+      </c>
+      <c r="M11" s="9">
+        <v>269</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>399.99</v>
+      </c>
+      <c r="R11" s="9">
+        <v>399.99</v>
+      </c>
+      <c r="S11" s="9">
+        <v>399.99</v>
+      </c>
+      <c r="T11" s="9">
+        <v>170.97</v>
+      </c>
+      <c r="U11" s="9">
+        <v>164.97</v>
+      </c>
+      <c r="V11" s="9">
+        <v>176.97</v>
       </c>
     </row>
   </sheetData>
@@ -8528,7 +8794,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303223D0-B4CB-49AA-99CE-D17D229E45B9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8540,14 +8806,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF9DD02-7584-4E7B-8430-E8812C31F69E}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="28.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3">
       <c r="B1" s="10" t="s">
         <v>61</v>
       </c>
@@ -8555,7 +8821,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3">
       <c r="A2" s="10" t="s">
         <v>8</v>
       </c>
@@ -8566,7 +8832,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3">
       <c r="A3" s="10"/>
       <c r="B3" s="1" t="s">
         <v>11</v>
@@ -8575,7 +8841,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3">
       <c r="A4" s="10"/>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -8584,7 +8850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3">
       <c r="A5" s="10"/>
       <c r="B5" s="1" t="s">
         <v>14</v>
@@ -8593,7 +8859,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3">
       <c r="A6" s="10" t="s">
         <v>16</v>
       </c>
@@ -8602,21 +8868,21 @@
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3">
       <c r="A7" s="10"/>
       <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3">
       <c r="A8" s="10"/>
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3">
       <c r="A9" s="10" t="s">
         <v>20</v>
       </c>
@@ -8627,7 +8893,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3">
       <c r="A10" s="10"/>
       <c r="B10" s="1" t="s">
         <v>23</v>
@@ -8636,7 +8902,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3">
       <c r="A11" s="10"/>
       <c r="B11" s="1" t="s">
         <v>24</v>
@@ -8645,7 +8911,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3">
       <c r="A12" s="10" t="s">
         <v>25</v>
       </c>
@@ -8654,28 +8920,28 @@
       </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3">
       <c r="A13" s="10"/>
       <c r="B13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3">
       <c r="A14" s="10"/>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3">
       <c r="A15" s="10"/>
       <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3">
       <c r="A16" s="10" t="s">
         <v>30</v>
       </c>
@@ -8684,21 +8950,21 @@
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3">
       <c r="A17" s="10"/>
       <c r="B17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3">
       <c r="A18" s="10"/>
       <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3">
       <c r="A19" s="10" t="s">
         <v>34</v>
       </c>
@@ -8709,7 +8975,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3">
       <c r="A20" s="10"/>
       <c r="B20" s="1" t="s">
         <v>37</v>
@@ -8718,7 +8984,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3">
       <c r="A21" s="10"/>
       <c r="B21" s="1" t="s">
         <v>35</v>
@@ -8727,7 +8993,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3">
       <c r="A22" s="10"/>
       <c r="B22" s="1" t="s">
         <v>35</v>
@@ -8736,7 +9002,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3">
       <c r="A23" s="10"/>
       <c r="B23" s="1" t="s">
         <v>35</v>
@@ -8745,7 +9011,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3">
       <c r="A24" s="10" t="s">
         <v>42</v>
       </c>
@@ -8754,28 +9020,28 @@
       </c>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3">
       <c r="A25" s="10"/>
       <c r="B25" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3">
       <c r="A26" s="10"/>
       <c r="B26" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3">
       <c r="A27" s="10"/>
       <c r="B27" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3">
       <c r="A28" s="10" t="s">
         <v>47</v>
       </c>
@@ -8784,42 +9050,42 @@
       </c>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3">
       <c r="A29" s="10"/>
       <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3">
       <c r="A30" s="10"/>
       <c r="B30" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3">
       <c r="A31" s="10"/>
       <c r="B31" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3">
       <c r="A32" s="10"/>
       <c r="B32" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3">
       <c r="A33" s="10"/>
       <c r="B33" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3">
       <c r="A34" s="10" t="s">
         <v>54</v>
       </c>
@@ -8828,35 +9094,35 @@
       </c>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3">
       <c r="A35" s="10"/>
       <c r="B35" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3">
       <c r="A36" s="10"/>
       <c r="B36" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3">
       <c r="A37" s="10"/>
       <c r="B37" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3">
       <c r="A38" s="10"/>
       <c r="B38" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3">
       <c r="A39" s="10"/>
       <c r="B39" s="1" t="s">
         <v>60</v>

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12EFB80C-E6B0-4536-B229-24E19E2B89CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4BA4BE-3FF1-4ADC-90B4-85A17630F3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="74">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -409,8 +409,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -428,7 +428,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -528,6 +528,9 @@
                 <c:pt idx="15">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -584,6 +587,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>3.7250000000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.7749999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -678,6 +684,9 @@
                 <c:pt idx="15">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -734,6 +743,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>3.4249999999999998</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -828,6 +840,9 @@
                 <c:pt idx="15">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -884,6 +899,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>20.295000000000002</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>21.681999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -978,6 +996,9 @@
                 <c:pt idx="15">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1034,6 +1055,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>10.7</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>11.266999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1250,7 +1274,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1350,6 +1374,9 @@
                 <c:pt idx="15">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1406,6 +1433,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>20.541</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>20.707000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1500,6 +1530,9 @@
                 <c:pt idx="15">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1555,6 +1588,9 @@
                   <c:v>10.476000000000001</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>10.476000000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>10.476000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -1650,6 +1686,9 @@
                 <c:pt idx="15">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1705,6 +1744,9 @@
                   <c:v>6.58</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>6.58</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>6.58</c:v>
                 </c:pt>
               </c:numCache>
@@ -1922,7 +1964,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2022,6 +2064,9 @@
                 <c:pt idx="15">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2078,6 +2123,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2172,6 +2220,9 @@
                 <c:pt idx="15">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2228,6 +2279,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.1749999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2322,6 +2376,9 @@
                 <c:pt idx="15">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2378,6 +2435,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2472,6 +2532,9 @@
                 <c:pt idx="15">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2528,6 +2591,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>15.85</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>15.35</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4792,13 +4858,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:Y19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -5729,6 +5795,56 @@
       </c>
       <c r="P18" s="9">
         <v>10.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="11">
+        <v>46160</v>
+      </c>
+      <c r="B19" s="11">
+        <v>46167</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="9">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F19" s="9">
+        <v>3.1</v>
+      </c>
+      <c r="G19" s="9">
+        <v>3.7749999999999999</v>
+      </c>
+      <c r="H19" s="9">
+        <v>3.8</v>
+      </c>
+      <c r="I19" s="9">
+        <v>3.2</v>
+      </c>
+      <c r="J19" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="K19" s="9">
+        <v>34</v>
+      </c>
+      <c r="L19" s="9">
+        <v>18</v>
+      </c>
+      <c r="M19" s="9">
+        <v>21.681999999999999</v>
+      </c>
+      <c r="N19" s="9">
+        <v>12.5</v>
+      </c>
+      <c r="O19" s="9">
+        <v>10.7</v>
+      </c>
+      <c r="P19" s="9">
+        <v>11.266999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -5747,12 +5863,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6DA72B-EEC5-42C3-B327-5A9F9ACABB0A}">
   <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -6051,13 +6167,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:Y19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -6837,6 +6953,47 @@
         <v>4.8</v>
       </c>
       <c r="M18" s="9">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="11">
+        <v>46160</v>
+      </c>
+      <c r="B19" s="11">
+        <v>46167</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="9">
+        <v>22</v>
+      </c>
+      <c r="F19" s="9">
+        <v>16</v>
+      </c>
+      <c r="G19" s="9">
+        <v>20.707000000000001</v>
+      </c>
+      <c r="H19" s="9">
+        <v>11.5</v>
+      </c>
+      <c r="I19" s="9">
+        <v>8</v>
+      </c>
+      <c r="J19" s="9">
+        <v>10.476000000000001</v>
+      </c>
+      <c r="K19" s="9">
+        <v>9</v>
+      </c>
+      <c r="L19" s="9">
+        <v>4.8</v>
+      </c>
+      <c r="M19" s="9">
         <v>6.58</v>
       </c>
     </row>
@@ -6854,15 +7011,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:Y19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -7793,6 +7950,56 @@
       </c>
       <c r="P18" s="9">
         <v>15.85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="11">
+        <v>46160</v>
+      </c>
+      <c r="B19" s="11">
+        <v>46167</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="9">
+        <v>3.3</v>
+      </c>
+      <c r="F19" s="9">
+        <v>2.75</v>
+      </c>
+      <c r="G19" s="9">
+        <v>3.05</v>
+      </c>
+      <c r="H19" s="9">
+        <v>5.8</v>
+      </c>
+      <c r="I19" s="9">
+        <v>4.3</v>
+      </c>
+      <c r="J19" s="9">
+        <v>5.1749999999999998</v>
+      </c>
+      <c r="K19" s="9">
+        <v>8.4</v>
+      </c>
+      <c r="L19" s="9">
+        <v>6.7</v>
+      </c>
+      <c r="M19" s="9">
+        <v>7.65</v>
+      </c>
+      <c r="N19" s="9">
+        <v>16.2</v>
+      </c>
+      <c r="O19" s="9">
+        <v>13.5</v>
+      </c>
+      <c r="P19" s="9">
+        <v>15.35</v>
       </c>
     </row>
   </sheetData>
@@ -7810,14 +8017,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DFE18-E6A7-46E2-A20D-CA2E453C377B}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -8045,15 +8252,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
   <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="22" width="10.44140625" style="9" customWidth="1"/>
-    <col min="23" max="24" width="13.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="14.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="22" width="10.453125" style="9" customWidth="1"/>
+    <col min="23" max="24" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
     <col min="28" max="36" width="9" style="9"/>
     <col min="37" max="16384" width="9" style="5"/>
   </cols>
@@ -8794,7 +9001,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303223D0-B4CB-49AA-99CE-D17D229E45B9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8806,11 +9013,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF9DD02-7584-4E7B-8430-E8812C31F69E}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4BA4BE-3FF1-4ADC-90B4-85A17630F3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9B68B0-7489-432D-9BF3-D3E530AFAFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="74">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -409,8 +409,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -428,7 +428,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -531,6 +531,9 @@
                 <c:pt idx="16">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -590,6 +593,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>3.7749999999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.7949999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -687,6 +693,9 @@
                 <c:pt idx="16">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -745,6 +754,9 @@
                   <c:v>3.4249999999999998</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>3.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -843,6 +855,9 @@
                 <c:pt idx="16">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -902,6 +917,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>21.681999999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>22.181999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -999,6 +1017,9 @@
                 <c:pt idx="16">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1058,6 +1079,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>11.266999999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>11.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1274,7 +1298,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1377,6 +1401,9 @@
                 <c:pt idx="16">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1436,6 +1463,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>20.707000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>20.638000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1533,6 +1563,9 @@
                 <c:pt idx="16">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1591,6 +1624,9 @@
                   <c:v>10.476000000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>10.476000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>10.476000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -1689,6 +1725,9 @@
                 <c:pt idx="16">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1747,6 +1786,9 @@
                   <c:v>6.58</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>6.58</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>6.58</c:v>
                 </c:pt>
               </c:numCache>
@@ -1964,7 +2006,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2067,6 +2109,9 @@
                 <c:pt idx="16">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2126,6 +2171,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>3.05</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2223,6 +2271,9 @@
                 <c:pt idx="16">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2282,6 +2333,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>5.1749999999999998</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.9749999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2379,6 +2433,9 @@
                 <c:pt idx="16">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2438,6 +2495,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>7.65</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.4249999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2535,6 +2595,9 @@
                 <c:pt idx="16">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2594,6 +2657,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>15.35</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>14.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4858,13 +4924,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -5845,6 +5911,56 @@
       </c>
       <c r="P19" s="9">
         <v>11.266999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="11">
+        <v>46167</v>
+      </c>
+      <c r="B20" s="11">
+        <v>46174</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="9">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F20" s="9">
+        <v>3.3</v>
+      </c>
+      <c r="G20" s="9">
+        <v>3.7949999999999999</v>
+      </c>
+      <c r="H20" s="9">
+        <v>3.8</v>
+      </c>
+      <c r="I20" s="9">
+        <v>3.3</v>
+      </c>
+      <c r="J20" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="K20" s="9">
+        <v>35</v>
+      </c>
+      <c r="L20" s="9">
+        <v>18</v>
+      </c>
+      <c r="M20" s="9">
+        <v>22.181999999999999</v>
+      </c>
+      <c r="N20" s="9">
+        <v>12.5</v>
+      </c>
+      <c r="O20" s="9">
+        <v>10.7</v>
+      </c>
+      <c r="P20" s="9">
+        <v>11.5</v>
       </c>
     </row>
   </sheetData>
@@ -5862,13 +5978,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6DA72B-EEC5-42C3-B327-5A9F9ACABB0A}">
-  <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -6151,6 +6267,47 @@
       </c>
       <c r="M6" s="9">
         <v>10.45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" s="11">
+        <v>46142</v>
+      </c>
+      <c r="B7" s="11">
+        <v>46171</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="9">
+        <v>24.3</v>
+      </c>
+      <c r="F7" s="9">
+        <v>23.85</v>
+      </c>
+      <c r="G7" s="9">
+        <v>24.158000000000001</v>
+      </c>
+      <c r="H7" s="9">
+        <v>17.5</v>
+      </c>
+      <c r="I7" s="9">
+        <v>17.149999999999999</v>
+      </c>
+      <c r="J7" s="9">
+        <v>17.324999999999999</v>
+      </c>
+      <c r="K7" s="9">
+        <v>14.2</v>
+      </c>
+      <c r="L7" s="9">
+        <v>13.7</v>
+      </c>
+      <c r="M7" s="9">
+        <v>14.1</v>
       </c>
     </row>
   </sheetData>
@@ -6167,13 +6324,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -6994,6 +7151,47 @@
         <v>4.8</v>
       </c>
       <c r="M19" s="9">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="11">
+        <v>46167</v>
+      </c>
+      <c r="B20" s="11">
+        <v>46174</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="9">
+        <v>22</v>
+      </c>
+      <c r="F20" s="9">
+        <v>16</v>
+      </c>
+      <c r="G20" s="9">
+        <v>20.638000000000002</v>
+      </c>
+      <c r="H20" s="9">
+        <v>11.5</v>
+      </c>
+      <c r="I20" s="9">
+        <v>8</v>
+      </c>
+      <c r="J20" s="9">
+        <v>10.476000000000001</v>
+      </c>
+      <c r="K20" s="9">
+        <v>9</v>
+      </c>
+      <c r="L20" s="9">
+        <v>4.8</v>
+      </c>
+      <c r="M20" s="9">
         <v>6.58</v>
       </c>
     </row>
@@ -7011,15 +7209,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -8000,6 +8198,56 @@
       </c>
       <c r="P19" s="9">
         <v>15.35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="11">
+        <v>46167</v>
+      </c>
+      <c r="B20" s="11">
+        <v>46174</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="9">
+        <v>3.25</v>
+      </c>
+      <c r="F20" s="9">
+        <v>2.7</v>
+      </c>
+      <c r="G20" s="9">
+        <v>3</v>
+      </c>
+      <c r="H20" s="9">
+        <v>5.5</v>
+      </c>
+      <c r="I20" s="9">
+        <v>4.2</v>
+      </c>
+      <c r="J20" s="9">
+        <v>4.9749999999999996</v>
+      </c>
+      <c r="K20" s="9">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="L20" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="M20" s="9">
+        <v>7.4249999999999998</v>
+      </c>
+      <c r="N20" s="9">
+        <v>15.4</v>
+      </c>
+      <c r="O20" s="9">
+        <v>13.5</v>
+      </c>
+      <c r="P20" s="9">
+        <v>14.75</v>
       </c>
     </row>
   </sheetData>
@@ -8017,14 +8265,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DFE18-E6A7-46E2-A20D-CA2E453C377B}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -8251,16 +8499,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
-  <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AJ12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="22" width="10.453125" style="9" customWidth="1"/>
-    <col min="23" max="24" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="22" width="10.44140625" style="9" customWidth="1"/>
+    <col min="23" max="24" width="13.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="14.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="28" max="36" width="9" style="9"/>
     <col min="37" max="16384" width="9" style="5"/>
   </cols>
@@ -8984,6 +9232,65 @@
       </c>
       <c r="V11" s="9">
         <v>176.97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36">
+      <c r="A12" s="11">
+        <v>46171</v>
+      </c>
+      <c r="B12" s="11">
+        <v>46171</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0.4375</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="9">
+        <v>242</v>
+      </c>
+      <c r="F12" s="9">
+        <v>180.18</v>
+      </c>
+      <c r="G12" s="9">
+        <v>211.66</v>
+      </c>
+      <c r="H12" s="9">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="I12" s="9">
+        <v>115.7</v>
+      </c>
+      <c r="J12" s="9">
+        <v>133</v>
+      </c>
+      <c r="K12" s="9">
+        <v>249.99</v>
+      </c>
+      <c r="L12" s="9">
+        <v>249.99</v>
+      </c>
+      <c r="M12" s="9">
+        <v>249.99</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>399.99</v>
+      </c>
+      <c r="R12" s="9">
+        <v>399.99</v>
+      </c>
+      <c r="S12" s="9">
+        <v>399.99</v>
+      </c>
+      <c r="T12" s="9">
+        <v>174.79</v>
+      </c>
+      <c r="U12" s="9">
+        <v>174.79</v>
+      </c>
+      <c r="V12" s="9">
+        <v>174.79</v>
       </c>
     </row>
   </sheetData>
@@ -9001,7 +9308,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303223D0-B4CB-49AA-99CE-D17D229E45B9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9013,11 +9320,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF9DD02-7584-4E7B-8430-E8812C31F69E}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="28.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9B68B0-7489-432D-9BF3-D3E530AFAFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF52A7A-917C-4025-A1A0-C35ED0827565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="74">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -534,6 +534,9 @@
                 <c:pt idx="17">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -596,6 +599,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>3.7949999999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.8250000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -696,6 +702,9 @@
                 <c:pt idx="17">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -758,6 +767,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.5129999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -858,6 +870,9 @@
                 <c:pt idx="17">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -920,6 +935,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>22.181999999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>24.318000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1020,6 +1038,9 @@
                 <c:pt idx="17">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1082,6 +1103,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>12.233000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1404,6 +1428,9 @@
                 <c:pt idx="17">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1466,6 +1493,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>20.638000000000002</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20.683</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1566,6 +1596,9 @@
                 <c:pt idx="17">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1628,6 +1661,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>10.476000000000001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10.48</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1728,6 +1764,9 @@
                 <c:pt idx="17">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1789,6 +1828,9 @@
                   <c:v>6.58</c:v>
                 </c:pt>
                 <c:pt idx="17">
+                  <c:v>6.58</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>6.58</c:v>
                 </c:pt>
               </c:numCache>
@@ -2112,6 +2154,9 @@
                 <c:pt idx="17">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2174,6 +2219,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.9750000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2274,6 +2322,9 @@
                 <c:pt idx="17">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2336,6 +2387,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>4.9749999999999996</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.9249999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2436,6 +2490,9 @@
                 <c:pt idx="17">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2498,6 +2555,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>7.4249999999999998</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7.375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2598,6 +2658,9 @@
                 <c:pt idx="17">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2660,6 +2723,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>14.75</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>14.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4924,7 +4990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y20"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
@@ -5961,6 +6027,56 @@
       </c>
       <c r="P20" s="9">
         <v>11.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="11">
+        <v>46174</v>
+      </c>
+      <c r="B21" s="11">
+        <v>46181</v>
+      </c>
+      <c r="C21" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="F21" s="9">
+        <v>3.45</v>
+      </c>
+      <c r="G21" s="9">
+        <v>3.8250000000000002</v>
+      </c>
+      <c r="H21" s="9">
+        <v>3.8</v>
+      </c>
+      <c r="I21" s="9">
+        <v>3.3</v>
+      </c>
+      <c r="J21" s="9">
+        <v>3.5129999999999999</v>
+      </c>
+      <c r="K21" s="9">
+        <v>40</v>
+      </c>
+      <c r="L21" s="9">
+        <v>20</v>
+      </c>
+      <c r="M21" s="9">
+        <v>24.318000000000001</v>
+      </c>
+      <c r="N21" s="9">
+        <v>14</v>
+      </c>
+      <c r="O21" s="9">
+        <v>11</v>
+      </c>
+      <c r="P21" s="9">
+        <v>12.233000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -6324,7 +6440,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y20"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
@@ -7192,6 +7308,47 @@
         <v>4.8</v>
       </c>
       <c r="M20" s="9">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="11">
+        <v>46174</v>
+      </c>
+      <c r="B21" s="11">
+        <v>46181</v>
+      </c>
+      <c r="C21" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="9">
+        <v>22.5</v>
+      </c>
+      <c r="F21" s="9">
+        <v>16.5</v>
+      </c>
+      <c r="G21" s="9">
+        <v>20.683</v>
+      </c>
+      <c r="H21" s="9">
+        <v>11.5</v>
+      </c>
+      <c r="I21" s="9">
+        <v>8.5</v>
+      </c>
+      <c r="J21" s="9">
+        <v>10.48</v>
+      </c>
+      <c r="K21" s="9">
+        <v>9</v>
+      </c>
+      <c r="L21" s="9">
+        <v>4.8</v>
+      </c>
+      <c r="M21" s="9">
         <v>6.58</v>
       </c>
     </row>
@@ -7209,7 +7366,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y20"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
@@ -8248,6 +8405,56 @@
       </c>
       <c r="P20" s="9">
         <v>14.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="11">
+        <v>46174</v>
+      </c>
+      <c r="B21" s="11">
+        <v>46181</v>
+      </c>
+      <c r="C21" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="9">
+        <v>3.25</v>
+      </c>
+      <c r="F21" s="9">
+        <v>2.7</v>
+      </c>
+      <c r="G21" s="9">
+        <v>2.9750000000000001</v>
+      </c>
+      <c r="H21" s="9">
+        <v>5.5</v>
+      </c>
+      <c r="I21" s="9">
+        <v>4.2</v>
+      </c>
+      <c r="J21" s="9">
+        <v>4.9249999999999998</v>
+      </c>
+      <c r="K21" s="9">
+        <v>8</v>
+      </c>
+      <c r="L21" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="M21" s="9">
+        <v>7.375</v>
+      </c>
+      <c r="N21" s="9">
+        <v>15.2</v>
+      </c>
+      <c r="O21" s="9">
+        <v>13.5</v>
+      </c>
+      <c r="P21" s="9">
+        <v>14.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF52A7A-917C-4025-A1A0-C35ED0827565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF6255ED-9EA4-4B2D-A07D-83574D2F5C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="74">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -409,8 +409,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -428,7 +428,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1322,7 +1322,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2048,7 +2048,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4991,12 +4991,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -6095,12 +6095,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6DA72B-EEC5-42C3-B327-5A9F9ACABB0A}">
   <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -6441,12 +6441,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
   <dimension ref="A1:Y21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -7367,14 +7367,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
   <dimension ref="A1:Y21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -8472,14 +8472,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DFE18-E6A7-46E2-A20D-CA2E453C377B}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -8689,8 +8689,45 @@
       <c r="Y4" s="4"/>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
+      <c r="A5" s="6">
+        <v>46139</v>
+      </c>
+      <c r="B5" s="6">
+        <v>46139</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="9">
+        <v>278</v>
+      </c>
+      <c r="F5" s="9">
+        <v>265</v>
+      </c>
+      <c r="G5" s="9">
+        <v>270.10000000000002</v>
+      </c>
+      <c r="H5" s="9">
+        <v>177</v>
+      </c>
+      <c r="I5" s="9">
+        <v>165</v>
+      </c>
+      <c r="J5" s="9">
+        <v>170.2</v>
+      </c>
+      <c r="K5" s="9">
+        <v>110</v>
+      </c>
+      <c r="L5" s="9">
+        <v>101</v>
+      </c>
+      <c r="M5" s="9">
+        <v>104.6</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8707,15 +8744,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
   <dimension ref="A1:AJ12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="22" width="10.44140625" style="9" customWidth="1"/>
-    <col min="23" max="24" width="13.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="14.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="22" width="10.453125" style="9" customWidth="1"/>
+    <col min="23" max="24" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
     <col min="28" max="36" width="9" style="9"/>
     <col min="37" max="16384" width="9" style="5"/>
   </cols>
@@ -9515,7 +9552,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303223D0-B4CB-49AA-99CE-D17D229E45B9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9527,11 +9564,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF9DD02-7584-4E7B-8430-E8812C31F69E}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
